--- a/Website/visit_binh_dinh/homepage/destination_1.xlsx
+++ b/Website/visit_binh_dinh/homepage/destination_1.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27602"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\6_Spring24\RES\Recommender\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dat\Code\Python\Project\ResFes24\Recommendation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337FEF5C-2AF8-443F-971F-6DBBE3739C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="984" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="154">
   <si>
     <t>name</t>
   </si>
@@ -325,149 +324,170 @@
     <t>Tháp Bánh Ít là cụm tháp gồm 4 tòa tháp kết hợp với nhau, nằm trên một ngọn núi cách mặt nước biển 100m. Nhìn từ xa, các tòa tháp tựa hình dạng của chiếc bánh ít – một đặc sản của Bình Định. Nhiều người đánh giá Tháp Bánh Ít mang những nét kiến trúc phong phú và đa dạng nhất, nó là sự giao hòa đường nét và điêu khắc của nghệ thuật Chăm kết hợp với tính riêng của miền đất võ. Quần thể có một tháp chính cao tầm 20m ở trung tâm đồi và 3 tháp nhỏ xung quanh, mặt tháp hướng về phía Đông. Đường lên đồi là những bậc thang hệt như đang bước lên cổng trời. Đến với tháp Bánh Ít để cảm nhận được nét văn hóa đầy độc đáo.</t>
   </si>
   <si>
-    <t>ĐỊA_ĐIỂM TRẢI_NGHIỆM HOẠT_ĐỘNG BẢO_TỒN ĐỘNG_VẬT THIÊN_NHIÊN BÃI_CỎ ĐÁ ĐẸP CHỤP_ẢNH TRẺ_EM GIA_ĐÌNH ĐI_BỘ</t>
-  </si>
-  <si>
     <t>Là một quần thể du lịch nghỉ dưỡng sinh thái, FLC Resort đã và đang nhận được đánh giá rất tốt từ nhiều du khách bởi phong cách chuyên nghiệp, thiết kế đẹp. Bạn có thể chọn Resort làm điểm lưu trú khi du lịch Quy Nhơn hoặc chỉ tham quan với giá vé 75.000/1 người cho đi bộ và 175.000/ 1 người cho đi xe điện. Diện tích resort rất rộng vơi hơn 1.300 ha ôm trọn thắng cảnh eo gió.</t>
   </si>
   <si>
-    <t>ĐỊA_ĐIỂM DU_LỊCH NGHỈ_DƯỠNG PHONG_CẢNH THIÊN_NHIÊN THƯ_GIÃN TRẢI_NGHIỆM RESORT CAO_CẤP BIỂN BƠI_LỘI</t>
-  </si>
-  <si>
     <t>Cũ mà không cũ chính là những từ dành cho khu du lịch này. Dù đã đưa vào hoạt động khá lâu, nhưng đến nay Ghềnh Ráng – Tiên Sa vẫn thu hút không ít khách du lịch bởi nét riêng của nó. Một số địa điểm nổi bật của khu du lịch này là Bãi tắm Hoàng Hậu (hay còn gọi là Bãi Trứng) với những khối đá to tròn độc đáo san sát nhau chạy dọc bờ biển xanh, ngôi mộ của thi sĩ Hàn Mạc Tử với những kỷ vật và câu chuyện về cuộc đời ông. Ngoài ra, Ghềnh ráng còn có những khu vực, khu chòi thích hợp để tổ chức picnic, khu trò chơi dân gian, nhà thờ trắng cực đẹp,… Có thể nói là có khá nhiều thứ để du khách có thể khám phá khi đến đây.</t>
   </si>
   <si>
-    <t>ĐỊA_ĐIỂM DU_LỊCH HẤP_DẪN CỘNG_ĐỒNG ĐẶC_BIỆT ĐỘC_ĐÁO ĐÁ BIỂN CỔ_XƯA VĂN_HÓA DI_TÍCH DI_SẢN LỊCH_SỬ NGHỆ_THUẬT CẮM_TRẠI NGOÀI_TRỜI DÂN_GIAN</t>
-  </si>
-  <si>
-    <t>ĐỊA_ĐIỂM DU_LỊCH BIỂN BƠI_LỘI LẶN SAN_HÔ PHONG_CẢNH HOANG_SƠ VUI_CHƠI THUYỀN CHỤP_ẢNH HẤP_DẪN GIA_ĐÌNH BẠN_BÈ</t>
-  </si>
-  <si>
-    <t>ĐỊA_ĐIỂM DU_LỊCH BIỂN SAN_HÔ BƠI_LỘI CÁT ĐÁ HOANG_SƠ HÙNG_VĨ NGOÀI_TRỜI VUI_CHƠI THƯ_GIÃN CHỤP_ẢNH ĐẸP PHONG_CẢNH BẠN_BÈ GIA_ĐÌNH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ĐỊA_ĐIỂM HẤP_DẪN DU_LỊCH PHONG_CẢNH CHỤP_ẢNH ĐẸP CON_ĐƯỜNG ĐỘC_ĐÁO NÚI ĐÁ THIÊN_NHIÊN GIA_ĐÌNH BẠN_BÈ </t>
-  </si>
-  <si>
-    <t>ĐỊA_ĐIỂM THIÊN_NHIÊN ĐẸP THƯ_GIÃN PHONG_CẢNH HOANG_SƠ YÊN_BÌNH CHỤP_ẢNH GIA_ĐÌNH BẠN_BÈ</t>
-  </si>
-  <si>
-    <t>CHÙA TÔN_GIÁO TÂM_LINH NỔI_TIẾNG KIẾN_TRÚC HÙNG_VĨ TRẢI_NGHIỆM ĐỘC_ĐÁO ĐẶC_BIỆT GIA_ĐÌNH BẠN_BÈ</t>
-  </si>
-  <si>
-    <t>KIẾN_TRÚC LỊCH_SỬ ĐỘC_ĐÁO ĐẶC_BIỆT ĐẶC_SẢN VĂN_HÓA GIA_ĐÌNH BẠN_BÈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHÙA TÔN_GIÁO TÂM_LINH NỔI_TIẾNG KIẾN_TRÚC ĐỘC_ĐÁO ĐẶC_BIỆT HẤP_DẪN CỔ_XƯA TRUYỀN_THỐNG GIA_ĐÌNH </t>
-  </si>
-  <si>
-    <t>KIẾN_TRÚC ĐỘC_ĐÁO ĐẶC_BIỆT TÂM_LINH HẤP_DẪN BÃI_CỎ THIÊN_NHIÊN CON_ĐƯỜNG ĐÁ TÔN_GIÁO YÊN_BÌNH CỔ_XƯA GIA_ĐÌNH</t>
-  </si>
-  <si>
     <t>Nằm ngay trong thành phố Quy Nhơn, du khách có thể dễ dàng di chuyển đến Tháp Đôi để chiêm ngưỡng kiến trúc còn sót lại của văn hóa Chăm Pa. Tháp đôi bao gồm hai toà tháp nằm kề nhau gọi là Tháp Nam và Tháp Bắc. Dù trải qua thời gian dài nhưng công trình này vẫn còn nang hơi thở cổ xưa và độc đáo từ kiến trúc tổng thể đến từng đường nét, hoa văn, màu gạch của người Chăm. Dù là nằm trong lòng thành phố như Tháp Đôi vẫn còn đó không khí xưa cũ huyền diệu giữa không gian hiện đại.</t>
   </si>
   <si>
-    <t xml:space="preserve">ĐỊA_ĐIỂM DU_LỊCH THÀNH_PHỐ TRẢI_NGHIỆM THƯỞNG_THỨC KIẾN_TRÚC ĐỘC_ĐÁO ĐẶC_BIỆT CỔ_XƯA TRUYỀN_THỐNG LỊCH_SỬ DI_TÍCH GIA_ĐÌNH </t>
-  </si>
-  <si>
     <t>Không phải là một địa điểm quá nổi tiếng với du khách, tuy nhiên, nếu có thời gian bạn nên ghé bảo tàng Quang Trung để có thể hiểu rõ hơn về vị vua Quang Trung – Nguyễn Huệ nổi tiếng một thời của đất nước, cũng như lịch sử của thời đại Tây Sơn kiêu hùng. Bảo tàng hiện lưu giữ lại những hiện vật cùng thông tin khá chi tiết về thời đại này. Đây là một địa điểm không thể bỏ qua cho một chuyến du lịch văn hóa, tìm về cội nguồn. Tại đây, bạn còn có thể tham gia thưởng thức ca múa trống trận, múa võ,…</t>
   </si>
   <si>
-    <t xml:space="preserve">ĐỊA_ĐIỂM DU_LỊCH BẢO_TÀNG TRẢI_NGHIỆM LỊCH_SỬ DI_TÍCH DI_SẢN VĂN_HÓA THƯỞNG_THỨC BIỂU_DIỄN TRUYỀN_THỐNG SỰ_KIỆN LỄ_HỘI GIA_ĐÌNH </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ĐỊA_ĐIỂM DU_LỊCH THIÊN_NHIÊN PHONG_CẢNH HOANG_SƠ HÙNG_VĨ BÍ_ẨN HẤP_DẪN LÃNG_MẠN ĐÁ ĐỘC_ĐÁO ĐẶC_BIỆT </t>
-  </si>
-  <si>
     <t>Tuy chỉ là một quán cafe ven biển nhưng từ khi được xây dựng đến nay, Surf Bar đã trở thành một trong những địa điểm không thể bỏ qua khi du lịch Quy Nhơn. Với không gian rộng thoáng, được thiết kế như một góc trời Tây lãng mạn, nhẹ nhàng trên bờ cát, du khách sẽ có những giây phút thư giãn, vừa thưởng thức cafe vừa hòa mình với gió biển, nghe sóng vỗ rì rào. Quán được bài trí đơn giản với một quầy bar bằng gỗ, menu nước uống đa dạng, xung quanh là bàn ghế gỗ đơn giản, cổng vào bắt mắt. Tuy đơn giản nhưng mỗi góc đều rất đẹp và thoáng đãng, về đêm lại lung linh ánh đèn như một bữa tiệc ngoài trời. Được bình chọn là quán cafe đẹp nhất Quy Nhơn, Surf Bar chắc chắn sẽ làm bạn hài lòng.</t>
   </si>
   <si>
-    <t>CÀ_PHÊ BIỂN NGOÀI_TRỜI ĐỘC_ĐÁO ĐẶC_BIỆT THƯỞNG_THỨC PHONG_CẢNH LÃNG_MẠN THƯ_GIÃN HOÀNG_HÔN GIA_ĐÌNH BẠN_BÈ</t>
-  </si>
-  <si>
-    <t>ĐỊA_ĐIỂM ĐI_BỘ HOẠT_ĐỘNG BÌNH_MINH HOÀNG_HÔN CHỤP_ẢNH THƯ_GIÃN ĐÊM NHỘN_NHỊP</t>
-  </si>
-  <si>
     <t>Dù không lớn và hùng vĩ như Bàu Trắng – Bình Thuận, nhưng đồi cát Phương Mai vẫn được xem là một bức tranh cát khổng lồ đầy mê hoặc tựa như một tiểu sa mạc, xứng đáng để du khách ghé thăm khi đến Quy Nhơn.</t>
   </si>
   <si>
-    <t>ĐỊA_ĐIỂM CÁT HÙNG_VĨ HOANG_SƠ HẤP_DẪN TRẢI_NGHIỆM NGOẠI_Ô</t>
-  </si>
-  <si>
-    <t>ĐỊA_ĐIỂM NỔI_TIẾNG ĐỘC_ĐÁO ĐẶC_BIỆT HÙNG_VĨ CON_ĐƯỜNG THÀNH_PHỐ HÒN_ĐẢO PHƯỢT THƯỞNG_THỨC PHONG_CẢNH HOÀNG_HÔN ĐẸP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIẾN_TRÚC TÂM_LINH NÚI TRẢI_NGHIỆM VĂN_HÓA TRUYỀN_THỐNG LỊCH_SỬ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ĐỊA_ĐIỂM DU_LỊCH VUI_CHƠI HẤP_DẪN CỘNG_ĐỒNG HOẠT_ĐỘNG NGOÀI_TRỜI TRẢI_NGHIỆM CHỤP_ẢNH BƠI_LỘI THỂ_THAO GIA_ĐÌNH </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ĐỊA_ĐIỂM DU_LỊCH TÂM_LINH NỔI_TIẾNG NÚI BIỂN KIẾN_TRÚC VĂN_HÓA NGHỆ_THUẬT DÂN_GIAN TÔN_GIÁO TRUYỀN_THỐNG </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRẢI_NGHIỆM LÀNG ĐỘC_ĐÁO ĐẶC_BIỆT HẤP_DẪN HOẠT_ĐỘNG NÚI BIỂN CHỤP_ẢNH NGOẠI_Ô THIÊN_NHIÊN PHONG_CẢNH </t>
-  </si>
-  <si>
     <t>Mũi Vi Rồng hay còn gọi là Mũi Rồng nằm khá xa trung tâm thành phố (hơn 70km), tuy nhiên, bạn sẽ không hối hận khi quyết định khám phá long mạch chốn nhân gian này. Nhìn từ xa, Mũi Vĩ Rồng có hình dáng của một con rồng được thiên nhiên chạm trổ và điêu khắc thành, đây chính là một tuyệt tác của tự nhiên.</t>
   </si>
   <si>
-    <t xml:space="preserve">ĐỊA_ĐIỂM NGOẠI_Ô TRẢI_NGHIỆM HOẠT_ĐỘNG BÍ_ẨN HÙNG_VĨ MẠO_HIỂM THIÊN_NHIÊN NÚI THỂ_THAO </t>
-  </si>
-  <si>
-    <t>ĐỊA_ĐIỂM DU_LỊCH BIỂN BƠI_LỘI HẤP_DẪN RIÊNG_TƯ HOANG_SƠ LÀNG_CHÀI YÊN_BÌNH THUYỀN CON_ĐƯỜNG TÂM_LINH TRẢI_NGHIỆM LỊCH_SỬ TRUYỀN_THỐNG</t>
-  </si>
-  <si>
     <t>Nhà thờ Làng Sông là một nhà thờ cổ mang hơi thở mộc mạc, trầm mặc của năm tháng. Đi từ thành phố Quy Nhơn khoảng 20km, băng qua những đoạn đường quê thơm ngát hương lúa, nhà thờ hiện lên giữa những tán cây cao hàng trăm tuổi. Kiến trúc nhà thờ là sự duyên dáng của phong cách Gothic, sự cổ kính của từng đường nét, sự thoáng đãng của khuôn viên, sự uy nghiêm của những dãy hành lang với nét chạm khắc trên tường, trên cửa và sự tĩnh lặng của những dãy nhà phủ đầy rêu phong. Không chỉ thu hút nhiều du khách, nhà thờ Làng Sông còn là cảm hứng của không ít các nhiếp ảnh gia khi đến mảnh đất miền trung này.</t>
   </si>
   <si>
     <t>Du lịch Quy Nhơn đâu chỉ có biển. Quy Nhơn còn có ba ngọn núi nổi tiếng là núi Bà Hỏa, núi Xuân Vân, núi Vũng Chua. Trong đó, núi Vũng chua là một địa điểm thích hợp cho những trải nghiệm leo núi không quá khó khăn nguy hiểm như cũng không kém phần hoang dã, hấp dẫn. Đường lên núi Vũng Chua bạn có thể lựa chọn đi xe máy hoặc đi bộ, du khách sẽ được thả mình trên những con dốc, những khúc cua tuyệt đẹp.</t>
   </si>
   <si>
-    <t>ĐỊA_ĐIỂM ĐỀN_THỜ TÂM_LINH CỔ_XƯA KIẾN_TRÚC ĐỘC_ĐÁO ĐẶC_BIỆT TRẢI_NGHIỆM VĂN_HÓA NGHỆ_THUẬT CHỤP_ẢNH GIA_ĐÌNH BẠN_BÈ</t>
-  </si>
-  <si>
-    <t>ĐỊA_ĐIỂM HÙNG_VĨ NÚI CÁT HẢI_SẢN ĐẶC_BIỆT ĐỘC_ĐÁO KHÓ_QUÊN TRẢI_NGHIỆM HOẠT_ĐỘNG THUYỀN LÃNG_MẠN GIA_ĐÌNH CẶP_ĐÔI</t>
-  </si>
-  <si>
-    <t>ĐỊA_ĐIỂM DU_LỊCH THIÊN_NHIÊN HÙNG_VĨ SUỐI THÁC_NƯỚC HOANG_SƠ HẤP_DẪN LÃNG_MẠN THUYỀN THƯ_GIÃN YÊN_BÌNH CHỤP_ẢNH BẠN_BÈ</t>
-  </si>
-  <si>
-    <t>ĐỊA_ĐIỂM DU_LỊCH BIỂN BÍ_ẨN HOANG_SƠ CÁT PHONG_CẢNH YÊN_BÌNH THƯ_GIÃN TRẢI_NGHIỆM CHỤP_ẢNH BẠN_BÈ CẶP_ĐÔI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ĐỊA_ĐIỂM DI_TÍCH DI_SẢN LỊCH_SỬ TRUYỀN_THỐNG CỔ_XƯA ĐỀN_THỜ VĂN_HÓA TRẢI_NGHIỆM </t>
-  </si>
-  <si>
     <t>Bãi Xép nằm trong 16 điểm ở Châu Á được trang Business Insider đánh giá là “hòn ngọc bí ẩn” với tiềm năng phát triển du lịch. Đây là một làng chài nhỏ cách thành phố Quy Nhơn hơn 10km, mang vẻ mộc mạc hấp dẫn của thiên nhiên, thanh bình của một làng chài truyền thống và hoang sơ của nắng gió miền Trung. Tuy không nhộn nhịp như những điểm du lịch khác nhưng Làng Chài Bãi Xép đáng để du khách thưởng thức, không chỉ bởi bờ cát vàng lung linh, màu biển xanh ngắt hay những tảng đá nguyên sơ kỳ thú mà còn là những trải nghiệm thú vị như đi thúng trên biển, lặn bắt tôm ốc và cả một homestay siêu chất lừ. Là một trong những bãi biển đẹp nhất Quy Nhơn, nơi đây cũng là địa điểm lý tưởng để ngắm hoàng hôn trên biển đẹp ngất ngây.</t>
   </si>
   <si>
-    <t>ĐỊA_ĐIỂM DU_LỊCH BIỂN CÁT ĐÁ BƠI_LỘI LÀNG_CHÀI NGOẠI_Ô HOANG_SƠ HẤP_DẪN THIÊN_NHIÊN YÊN_BÌNH TRUYỀN_THỐNG THƯỞNG_THỨC TRẢI_NGHIỆM HOẠT_ĐỘNG PHONG_CẢNH HOÀNG_HÔN ĐẸP</t>
-  </si>
-  <si>
     <t>Nằm tựa lưng bên những vách núi cao và phía trước mặt là biển xanh, Hải Giang giống như một ốc đảo kỳ bí lọt thỏm giữa thiên nhiên hùng vĩ. Chỉ rộng 120 ha nhưng biển Hải Giang đủ đẹp để làm say lòng bất cứ ai. Đến với Hải Giang là đến với những giờ phút thư giãn, tránh xa náo nhiệt của cuộc sống ngoài kia. Du khách sẽ được quyện mình trong không khi yên ả của những người dân nơi đây, thỏa sức vẫy vùng trong làn nước xanh, phơi mình trên bãi cát vàng, lặn ngắm thế giới dưới mặt nước hay mua hải sản từ người dân và trải nghiệm tự mình chuẩn bị một bữa tiệc nướng ngoài trời dân dã.</t>
   </si>
   <si>
-    <t>ĐỊA_ĐIỂM NÚI LEO_NÚI THỂ_THAO HOẠT_ĐỘNG MẠO_HIỂM HOANG_DÃ HẤP_DẪN CHỤP_ẢNH TRẢI_NGHIỆM PHONG_CẢNH THÀNH_PHỐ BẠN_BÈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ĐỊA_ĐIỂM YÊN_BÌNH THƯ_GIÃN NGOẠI_Ô THÀNH_PHỐ VĂN_HÓA NGHỆ_THUẬT DI_TÍCH DI_SẢN NGHỆ_THUẬT NGOÀI_TRỜI TRẢI_NGHIỆM BẠN_BÈ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ĐỊA_ĐIỂM PHONG_CẢNH NÚI BIỂN HÒN_ĐẢO BÍ_ẨN THIÊN_NHIÊN HÙNG_VĨ HẤP_DẪN THƯ_GIÃN YÊN_BÌNH BƠI_LỘI LẶN HẢI_SẢN TRẢI_NGHIỆM CẮM_TRẠI NGOÀI_TRỜI  </t>
-  </si>
-  <si>
-    <t>ĐỊA_ĐIỂM DU_LỊCH HOẠT_ĐỘNG QUẢNG_TRƯỜNG THÀNH_PHỐ NHỘN_NHỊP VUI_CHƠI TRẺ_EM THƯ_GIÃN ĐI_BỘ LỄ_HỘI SỰ_KIỆN BIỂU_DIỄN ĐẶC_BIỆT</t>
-  </si>
-  <si>
-    <t>ĐỊA_ĐIỂM PHONG_CẢNH ĐẸP HẤP_DẪN BÃI_CỎ THIÊN_NHIÊN NÚI ĐÁ LÃNG_MẠN YÊN_BÌNH CẮM_TRẠI NGOÀI_TRỜI HOÀNG_HÔN GIA_ĐÌNH BẠN_BÈ</t>
+    <t>MỘ THI NHÂN HÀN MẶC TỬ</t>
+  </si>
+  <si>
+    <t>Mộ thi sĩ Hàn Mặc Tử tọa lạc trên ngọn đồi Thi Nhân nổi tiếng ở Quy Nhơn. Để đến được địa điểm này bạn có thể xuất phát từ trung tâm công viên thành phố nơi có bức tượng Hoàng Đế Quang Trung sừng sững giữa đất trời, mang phong thái uy nghiêm được xây từ năm 1976, từ đây bạn sẽ di chuyển theo hướng Tây Nam phía bờ biển chừng 3km sẽ đến xóm biển Gành Ráng nằm bên phía tay phải. Băng qua con đường vào xóm chài Gành Ráng bạn sẽ tới một khi chợ nhỏ của người dân địa phương, ở khu này có một cây cầu nhỏ bắc ngang qua quán thủy tạ Mai Đình. Từ đây, con đường dẫn tới nơi yên nghỉ của Hàn Mặc Tử bạn sẽ là một cây cầu nhỏ bắc qua suối Tiên mộng mơ, khi sang tới đầu bên kia của cây cầu bạn sẽ đi theo hướng tay trái để lên đồi Thi Nhân. Con đường nhỏ lên xuống ngọn đồi này được làm thành những bậc tam cấp bằng đá, với hai bên là những hàng cây được cắt tỉa thành hàng, nằm ẩn mình dưới những tán cây xanh, một con đường vô cùng thơ mộng được gọi tên là dốc Mộng Cầm.</t>
+  </si>
+  <si>
+    <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBxMTEhUTExMWFhUVGB4aGRgYGB0dHxobGiAaGBsYHRkaHSggGB4lHR0bITIhJSkrLi4uGR8zODMtNygwLysBCgoKDg0OGxAQGy0lICUvLS0tLTUvLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLTUtLS0tLS0tLS0tLS0tLf/AABEIALcBEwMBIgACEQEDEQH/xAAcAAACAgMBAQAAAAAAAAAAAAAEBQMGAAECBwj/xABDEAACAQIEBAMFBQUFCAMBAAABAhEDIQAEEjEFIkFRE2FxBjKBkaFCUrHR8BQjYsHhBxUzcpIkQ2OCorLS8RZT4oP/xAAaAQACAwEBAAAAAAAAAAAAAAABAgADBAUG/8QAKREAAgICAgICAgEEAwAAAAAAAAECEQMhEjEEQRNRImEyFFJxkQWB8f/aAAwDAQACEQMRAD8AfcNqfvFjqY+eLBpwi4Zwt8ump38asFOw0j4Ak9Os94w/rMKNINVMuRJE+7/D546EJfHGpHNyL5JXEgzJIUldxcefl/LFM9oMzq01CGRuosQYNr9PJjvbphpn+LFwdHTa5HwkHCD9qpsVWq+h2aNbDcGwBiJN+3W+M3lz+Rcf/CY4OO2cZrOf7Soqg+GonSNoYAzI3uTfy6HDXNVaeYBUBrXW42Fj5tt+OFvFqaqumTyE846jcAmYF5EHfphdwXM1gzMgDI06pB5SAYIgiJggH1GOcsrcpY3uJdx9kNfOFSQSQpnmAMTFrxIBn8dzOGuUNOoKSCqAdAZlXfxGa/M3QAAxuZXvgzidbL1sshoOqNmB4ZDAHwzGp5AMrAnbe0HCivlVy2aNJwXSpei6nnBWIq6dr3GnflHYTascYprsLRYOLVBlxTLLp59DPuANBaZ36HYfXFQzPtKHP7O6/uvFLl5Mon3QOpA6mcFe2fFBWVzPMuYUQCSI8JCLE9GFTpF8UVXMO3UiL+ZFvxxdGcqE47PUuEVKS0WzOXZqjNYKV06ipuQsb9fT4YI9nM8pRah5fEqEaTAgSFmZMkkj8BEXqj8eqU8nRydEaW0FnNtmlzE3B3J7AHvhj7LeONP7IEapaz8wWbkHS0iJme5iMaYeRTVdAePR6Ycu0TBxAyYb0pKDV70X0zE+WIqmXUjt5nG2Ob7M8sX0K4xkYH/vBBqLGFB94AwRGqR1MCxMbjC+l7S0m06VJJJBErKx3E/TEflY12xPjl9DYjHMYr+Z4tUqNKU2KqZjSZUi2olZGk3BkxHriwUKoaY6GDhsXkRm2kCUHFbMjGoxIxAEnYYwDF/JCEenGacSacCcWzy0KTVXnSsTHmQv88RypWwpXpExGK37aVG8EVKTA+GTqAM7HSTpHvQbG9pxX+O+0P7UtHQxTw6jFhOmelMgzzDSb+pwHVzD+J4i+8FYuQDzpCgqRF5sdgLd745/keXBpxNWPBJVJhq8WFWousimxUaBuAQJLQPdNuu8RaMWD2f4xNRqVYS6m2oWvuIiJW17zPTHn1bKgkqCS83BsSCbMAOw/A4e8MralBJNR0XSVFy/3GMT9kFZ+J97HFzPkjQ4lt4TxihSzdWhSqBxUcsQByhmEPTj/l1erHCnjfFlaqFqvpbL1qigKG5wyjQDB5SUO/dT0wu4Xkk8YVzqSorhn+6AtmvElvTebDCz2wzAbMNURWCPUVgzIV1FEVCRq5rEjoN+uMySc6FaGeb42c1UyqUNVPQxJVeUBQEWbbAHWIvZZxzxXjXiVq1FAGWyj7OrSQJaTJAliLb6eggrPYqgxqmqGpp4VEEs9496Ipggu0WAHYTvhfTrNSpMjg8zamsQ5BFtUkgwCYt3uZxqi+NpA4bCG4lLqlbXUoq0ikLWE9TYbxvsTti6+y1fMVqqzQEVElfDgaFB93TNx1m253x5wqrrljyBrGDzG0wOxmYm0xPXH0v7JUKa5WlUVdJqornuNQ1BZ7CYjGrDnlB1H/sf4lPsEy1VqFPw6g0EknpfbqD8MJuK8XW95w29ps1TqLpa8bdwe4OPEvaPLv41QHMsKaXubkQCQINzNtunTDTk5S/bLYpRVF0fiKkk6x88Zjz8ccFLkprKKTBZZO87m+MwPil9k+T9HtFCorDSxv0n5R54qntnx4U63h1W0zcT1FxPpMj4YruV9tc3q1DKtYRBkC8HmnYHv59cSZ/J5rNqNfhagwc0Ap5VF4DF5IvcgYeeRtJMpjFRk36GOXrhgGBEHYz/ADxFxEtzOgEG4P8AEogtPS83G/nhflMsJShTVVGodbyw6AnvPXr6Yb8c4L4FLVDPqZRC7qGmZUzyzfpGkTjL+eWLroMpK1QEOIAU28YKp1CSv3esoeg3/wBXbHVRUzFPQGAYkw4sabKCTezFDGx2g72wkr50qzAtqkdYFzBAksZ+Jm9xIgwog8MPqC6iQhNzJ+wzA3ESSCNr+RRKSYyDsp4gLVNCK9IDWABJsTr0nobHvYwCQBg7i2XVtDGdWnXTZbyIJ0RYRMG/f5y5Gnl6+XcvVWlmAWKsSQmy/uzPTSQN5LC3XC7hVd/GogAUglSVOqIHNqgnla5YCd5HbFkoU0T2c8arU8xQqVlpqlYeGzgGS49wsvUn3mJ3j0xXMjlpVYQMzVOUyfsAMQBIW8gSQdseie1fCcnTKrRVAUUtqkkGYKRcg2kEbT5nCuhwcOlNKU8gYwDyjXoElmiwAM+m+C5cdAor/s5wqrm8w/hhyqqxfRv6AmPIXO3fF79nMhXNDXSIpU6VQK4SJcmGqAkhuUBgbC8G+FVZKmTpHKUKlM+JzO4nUBpsjEG0AGwvJE23QZ3juhWo0j+7JUVCP96ybHc7neNgow3KnQT1XNcZp61WjVCZcnRqvzupWQjAjSIkajIJkYV8R9tkiukFoMK6+6ZMEBjEx/lF59MeS5/PmqwWiHp0geRNZm8AliLEn6CB5k9AoUKZiNh0idotExPWxPlgTzSj0LKOhzmOIMFVJYGw3J1XuTe1rWF/w74YSCNR0qWknc2giR1m39MLKR1tSMkLBEiCR+ieuN0AamZSlRIGuqlNeu8IxM9txM/HGSP5SVgSdnqfsvwmschVdZY5g6l6ciwBGqCdQ1GbbjFRzHFnoM9IMQxIJjdVVRBA8xuR2HWcezUyqUgqWRF0rHQAaR9MeP8A9ovCmUU8zpLItQ0X8gTyEnt0B7xjoXJQfF0yycE6QurcVqVCFNR5CgA6gPpIExA8/PHdHiFaiQQ7xA5SS3S9jsJEwO2KzSBUk26/jbG/20B5JkTcyewvG8T8fwxlU8idptk4KqotvC/aOo2ZVncKjcrAyFEwAR2PmenfFxzVOnXpOoKspBE7gEdbbxjyXL5jxGgbsdxa5JMSRPzw89nOOVcm5SrDUxaPn7nY2Jgi8Y34fLpcZ+yieB/yiU9+DVNZpEMHAMKwjYaj9JOOKfEKqtoJJsFA8u3c/qMWvO5suatRnLMWYsNIIX7UK6kgBRa97YUUVWoVQKpbUTDC0TJWALmepOwPljFklt/Ro9BGaYMlMhAGYjSdyQAQykg8stPT7u2OnzE05CkTKFbCF1cqmAOYGxsDacQ1svpQ+GypoUaqTk6lF3L6hAqCWK3uOWcRDOjYqp1uW1hubVtabXlZBG4n0z99C0G0+MeFqBFSSIJGkHWTcEtcWuDI74Az1SrVpE1cwH/ZwQiwBYlS0QL7A3PTE9HhzVAxenpMA6gbtczK3AEAiABzae+B8xwVC8LUYrqCsoAtY6m37q3Tqu84f40nYtB/DeIVKNCouWJWrnKiUaRkWp0QAzz0k2J9e2Fmboi9aqTo2WXJaqbanmSSNuuHQyfg5lGSYp0URmI1BS+hUVVPVm1n/mJO2KbxWvUZ21k7yR5+nz+uEgnJjJMkzGeaqw1WCCFUAAKCdh8T1x6FwP8AtGqUsmuWK66tJAKZHusPsox+yVHXYxvOPMstT1coEsfd9e3r284GLC0ZOmCGVqrGYMyliGJHQiwv54vnNQSS7Guuh8nHuJF5dabSLJKqZIsYLaiBaf1CapkKv7x61QiqyOQoYAyYBnTaCG2HxwNluF1qo8aqxVVBbUQNbASxI2LG86j87YK4fRSo+lURVBktUI90XJLHvEQOuDHLHlpWw3ZW1qx0X4gYzD/P5On4jRTi+1x9MZjoLGyvmj2HNez6BxUguwEAEwJiCx+9PY2+WEOfyZpIWCqtSoWU3AkjmiG3GwEEE/TFy4RxGnmKYqUzYzv5GJwi4wUrVVplpAMiI77C0yI+Nu2BmlFR17MsbvYq9kuGEzUzCMCwHhtyjU2x5vdkkCJ3nB3H+KjUfDdyyCNMkESbkXhzE+uFebz1TJnw7MrCGXTAiCYYTZj9SPOMLP2estJaorEoTJQqA3MNWkMASRHmItjn5ptRUYars0RjbtkubOVzFMCpT8NhFxTEsSdiAfLedz0OKjxLhmlv3TWG6kxzXuF3E2Aw4ra6ilgzGbKZBv2bUDMeZOFtTP1nQIyz1LaNJhRIkiQ0bRHbyxVHJK+y2iHh6s50MdJlRpmAbzIaI6fWe4Ll0vzMW7yYMLygeVreVu2BsrTlFJJaVGnVHLAMwfX5bbbdGq6KTp9DbaLW/X5Sc3JkonYEwVMDtFgAdwfQE+UgYJXMVIUodOlWC9o5um0yZnCPhPFGQmVmR1P3gZm3aBGG+ezGjLq6wSbaRIhiYEfCT5QMM2v4sDj+VHHEaIYPqJDdWB960Fp6ybD8gcVh8g7PoQFp92Lj6fKbYdq8qRb4mwE+Rnt369MR51GUBkU78zDYg9Nxb6/DFfyU6QvLYtylNqbNpDFrAws26wO82jB2XBV3uCoiSTO95kb38uvylU2VKUlmaCwOmbxqYNcTbePwx3l8wXDUrFiNI8yLgfMG/c4STckwXTCWyulHOxiQFBtq0gyOuxMDqDtInn2IK/ttBdJIDPzarSEc7Ad4i/bAWbzHKEeRfcWi957jb5Ya+yFel+3ZXSoBWpA7E1AUN+pCtN+o6YGC01f2Xcovo9l4ZUIyza4Jlo9Aur88VL2tzz/sWaBAhlKBRIuxA1m/TsIknF0zdPTl3HUtpHxKg/QY81/tAzhp5WsouXqhTPYMD69Bt5469WmxW2mjz7K5tGIQXAsOxMXP8M9BHznDb+4w6HQJb84tPXqfjhbw7g1R6yutJlRtxpsAb27iINtpxZ1zGh/CEgmDMWP3tW895m0TbHMy54w1Hsfkq2L+FcNbLgs5BvAM9oPu9Qd/lvjKudWo/NcXEtcGbGJ3Gm232j5YmfMjxCDUBhRPJ0YAhkbbrN77WtiPjnBmZiyke9YAXEgwN56D/WBjFblLlN0xW/oKr5gVKbFHCMeWzFbXN9O5uTe56RBhaeA5jSzJpZbmWsZ92zTJkHucVw1GFTQxup6xHr+pxbuFUq9VJsAoiR1PKStuZSytMwegsZxZL5MSVPX7FSaEmTyR0kVQsCCDBJbUBIB628uu4vgnw0VadvCf70DSGmVfbvIKtNpHYDQ4fDl9RUrIgz7txy9BttFhg45iZBAg3IIsfOI3j9bY0LLS0Nw+wQ0GDq+l0uZv/huCJH+U32iAQfLDWjTWSaYA2IEQTqgxHYCV9D8+ctVV10AnUsc09IKg/IESfuXucM8nwrxKYKGHKtEGNwYjsRIHwwrnq3okloLzlMQz9DO+3LrRQ38JR3HqRjz/ADfBm0AmC+oioSbvVP7xhc2CqSWNo0P3GLVUq1DGXgLBViQIvIsbXgi/e2B/7s00kBIYIXJiSahbSRN7qzAHcTpUSAGK14pOC2Mo6RWeC5FtD5gAwLUiV95t9ZtyoALk26YlzSJSbxs2fFr1FkU4jSxFqlTaf8vXftix13VdGu60hCp9551TpEAgWE2AiFGlhhbxmnTrMHKMahUDvENJJYnm5bbeQMYb5OUt9CySQtr8ReuuoapLNKg2gHVt5axfucK3YseZrA3ja/QAEjDKl7Pt9swAdJjaSJEHrfDfJ8BTlMyLFrG0kcm9+0+fTFsckI9C39HGfok1CYnb8BjMH5isQxAH1xmOn8rF4ok4BxqMo1FSQfFkEGGYMAgBA6W9DfBmTauUaqNQTpp2gWO0mI6zc4pGTISrrUjSLjrbYb364fVeLhKRLSA0aEWCTHU3IUXi+MGVNuw0hxneOmqRIAYL4ZN9WnoSxJHa/kcB1hAIJJBFrx0gG/f9bnCzK8UaqCunR5DtO3uyfrgx1JFjBufkB+AHwxVljKXbGSo7yuWWCZeSI1A3+7ttHYEH4YyjlSSw1NsRGkXvBNuu1oxxkZhgJEAtYTMCRHebfCfjKHJqKosWMD4Akkg7A2t3OKXfLsdOyCjwx6KlXdSBAi7C0ge5BPKYI7/DAZ1AQz3jaNgYII+F4wfTzDLSmowLAn4kC1iIEmJP474j4gKZsUkiNQ6iAIg9d974V5Jp/kLJ12L8rQ5hadLGfQxP8jja1zMEAidKgidyRqjyucMOBIviXBPQj7wPu/GbfH1wLlcvqdViWmw2uYj5Qfl541++XquyylXIhRqikjYsDEER8yLHpEfngsVj4UOsKSNjHvAc3W1o6Y5zhNGvN2aTpgAm5IgEb2P1xzxDPDRILaTJKluUzI0mnuD5/wBMZX+RmaA88CsEgQJ94zM+dvLbsMEZQgrRUBQ1whAEWOu5G12JnrjjLIKlK9118tz0BAMEeog9/OcNHUKQi6VKiVZ5A1bm8dO3oBhMk3/H2WKF9ifP5FyrBgC4JFuxuT8L4aexfs3TzJealVDT+4Yg37iQRYgjyx3xLJ2ol2AL1TJBP+EsEn+Hc74vXsl7PjK6mDM+sCdZHr0Axq8OMpb9DSjFdFqTiDaFVlDaRdjuxiNR8z/PFV43wCnmqyuxdApJCqVjUftQVP4xiwsbe6AfXEao0gkC3njqcVVC2eO5b2mddIALAxK/UfLacc5pK9apUVoptotS0kFyBJAB/hLNJsdNtowy9sPZ5Mk9BqTvLEmWK20aYIgDqeu+FnEc9mEqNXqw1QoBPLAEghhpHeCIII+U85ePCEv2MkE8AzIMrVUipTBQ2mUktDEW94t17RtiLN+0LFnppOn3ZMiJm5JjoDbrjWWr6yHUik7KWi+moesmxIkAlATt13xF7SUl8c6ICs6WAn39RC2uSCCI9O+KJYIufJkcb2J83liee1iQDa8abi9zBB3nDfhnEfDzL0oLLqYFdUAlSQLEwOvUzHpjviHDWoLR1sHRKj1msdopAAtf3tMeUzfAnBoqV6lRAoOmddQgeHrF2AEy25noR0wZVLG/YHpaH/E6AE6rMOUATaRMbX/raMJWqhiYkAx8N7Cfj9euJadQhm1rUdBImCCDEbTynYidoG+AuIZcK+hSYnlM9JI7X2YeRkYrwxaVMEGxjw8gOp33WJiQd1J+A9YHxaezvFfCreEx5RAiDy/wxvIuI88JuH0WVtWpSCpabyBB7jfc/DD2rw+lpq1XszLqkH7UDee8T8DgeRKNcTRtxpCn2l4kddQR/iMCCBsCBJuLk9vXHeU4ptSUFmCfZ+yTEKCYhi+kdtvUQtTqMyqpDBrSwsumSWnywFUyrUQzC7M3hKSCCS1ixAuABJnuQcWw4uKTJI7KlnEc1NbTJ5tw1TSN9TGdvd0jDt1LqOg8wAelgbfrpiCnwxaQKnabEDeAIuPicR5LPqoabEXue/l8OmMuSXL+PozOWziGXSoMBpEnt6xY2t64IrMyAFSSQYA6EQb36238/mQnFZXUBym8HqPkd538sCHPIwlTPkPsnYDe4/LrhVKT7QFKiXNE6jf9RjMbzNQ6jjMd5RdB1+ypZpNAOkyuqN7EiPLAykm5Pr3xdc9wZKohGAIOorpMAkKCQT75geW3rjWQ9jqYM1a4I30rvETBO0+fl1xzV5uNRtg5oVcLRQJY2YwF6/CPXBGWzc1OXUJmCALGSAD1IJIGHmV4FlFYsGJIggu6gINUE8ovPKAJ3OJ8rk1VIp0yajsdDPAJkEBgskAAyRMXA6YofnLegqxXScQatQcwaN9gehANxM3InbecZlTUastUwirI0sBzRaFtfcAgWw3Sgo0iUbVudW14J5exMbRY/HBTACkVhqAkiQZ98nSRdh0jv2xmj5FSuiRtPZXM9UgVgigaqtgfPVquSQAYH1xJxUMgDEtaJtAgWFuh6DfDhskuptFyTOqYUT23v8umF1QKSoZwYa8QdpsSYuN740TzRm04jT2zjhTaa6tcgmBzdJBgKfjaek4npAftFQJJasxp0xsULhmJgbn3V73a2GNTh9Cko0nWHLBTMgQCTrK3Zgug25ZaPLE+VzVKmNKLoqMJCI68x0wjTdtR1CBMcxuMZ35EqairTAovoXZeiV5dPOBvzXMNaASQZkfKeuKtxeqVGksLkz5E3b3hIM9MXSrm6jM1JVTUQSrJqdhAVdKumxMixA3I7YqvB8qDNZ31upYshMEssgCT1lZmOvle3x5NXKX+hIxpnXsprqEClzeEwciSCQTe4BAESs9JGLDlqHiV3qhGQKIA9/SrAQTMHVvEAxBvGIOGcSalrCtHiKSw3hQbC8dTc9hbE/Bc+SGP7vwkhajuSSbNphY06hY3PbC5ZTbckiyM7lTAeLExHNqAIBsQRAXTJMT52vve2PVMkZUdRb88efcSbLUzUZlhWWdVjJgudifs9OsXPXF+ylER5fHHS/46Vp6HyKgs4ycReEPP0xsUP1Jx0ysov9rGWLrQhhy+Ib//AMxHqcUbhVQAeGylkM7FQykyJVmBANp26TbHo/8AaNTDUadPSzMzEKBN2sII6i8xIuBjzdVVGYlfcAJCbRYXM+cT3PTbHN8jI+TX0MixU+GVB4WhmJo101I6hXCyp1G512nrtMCxmH2s4a4eotFJWiyT6+HS0lTN2BLbH73oWOf9oE/cU8s15Qku0iSNNhAIYWllI3I2xLmamkkioH1XUgmNQO+qIDCx6i3lbnryppbj2CU0loTUUq+F4TjU62cxq1E6tSMZAIXVpJmJDbxOIKPAKKuuksSNyjlQSBMSxIibXPVcMKtVaWXZXYio2rSEMjlnURvJk+9PXCtc0p5KynUCQ76pkfZKjqL7ec+k5yk21pFTlvRNVzKsdpUQpI0kSLKAep1dd7Y1SoUmUaghIMAklgGspuTJ1AA36+ZOG6ohWAtNU1EaVB1RsIAMKRym3be2FeeyLiqpQKhCyxVg46GxALM8kC5MRv2kMi/itDLRBkqGhCCVDfd3nTBJm8Trm+8CLxiSjxEVEemQAxF5JMkWJmbyZ+eCjlqioFVqdRomJuASpmwOsagRJxBksvSEK1MrUAXUzsRpK+9yg2EsIM7DytHNNNsMckk7RHl30kU0ty3cAXmDci/Yx5i18EjN0zKhSzczEgXYxBUnoIEkgRafLC3M1UDfuizKwA8QqRBnTeBYAT06+WOcgENRipuWOmFEEC1h28+lvizjrkLb9h/94FdK30z1kx8SN+nzwh4vlC1QkDlmDBH16fE4tf7CXollDBgNRgTYD6Sd7wAQQDBwEvB6hVZCxAk6gSxP2YWSTMna0fOvHljF2RlbzpdUJnyWdyOwjt/PAGQck+9C736mYA+Zw/4nkWRyrCQhKl4OnUdhcC9x0m+NDgaTAWTEWBN9yZ2A9YF8a1lgo79hr7HOcptrPMfkO3pjMcVydRHa3ytjeO0kqKeTO8jx5Kj6QpJDPoKiJICmJew67ycJeKZw6iFuWcw3iMZWxCgQRy3Xcna2IfZlqZr82ZWgi1A4DKxBJ5SsA2sYknbHHtLRoftLtQggPqjmAeTMAja/a3njhRxQjkr9FqghpwPL1SQ1RDpXmJWp+8FISTyBWv0LEdhacNuG8ZpMGOXUAEksR77NGoTJ1Eb3O5Bvim1+O5kOQFWm5I1AIpJIjTIYEsQO/S2GHDczm1YVqvikMjAaVA2IIkAAASO3TEyeM5K3X+C1R1oeJxNfEqUkYMzCZgqoaZKnlkmR7xkeeF+YzGUy5YGpWDCShWGEke6ebe5O9r744KLVCvFpKamte/LIJcki8iIsN5xyagEDRpp2lQ1okSeYgNcH5+gwkcSi/f7E/wAjqrxI1Mv4uoXUKCQupgbFmsb2E/8AqAxTlEkrKSAJuIgwNIIM2Ekf0h4gw0laYikwsotZb2AO0T3NjjVLOmjpUUl2Bj3izNzAgzeBB7ifK4WPX4hX5Dipn5Z6oIVjyanWGAuOt2sBAB6DyOEPEOJOhWt41OoykkCoTBBtIUEwwtBF4Ufdw7p5cEAghp31KCATaCFvEmJ+hAwwy/s3QgsU1aoJDgHYmw6hQTF5n54bDgSdsdQbKNX48aUmgSgdtUq56jSykQL9Zt3AGB3ziVqinUEkkeGJCpcHc6ixJJM9x5xj0T/49lAT+4pEXMFRAI8jMdRgSt7NZdTK0KRHVWUfHe46+Yt8NihFDfHSKDnXFlRi0A7k2i9u9rQYiTvvh5wXi+XpMjMoSoIRjz6SpIJq9AG08pBJBF46YeZ/2UosNVJRTtOmLeny/l3wFkuBRUpK4sh8tgdcW3v+OCsSnoHCtjn2jNMNp0OVqKI0agJYFdIQExYnbfVOLrVzS06TOTOnoI7x+rYXpl1qJIE9Z/Wx8sF+0I/2ep2i/wAxjbDHGH8VQjAV9qlMcm/dx+u+Jsj7SK9UJpK6pAJIItvceXfFdy9Vj9skDqdQsb+h2HyGO+Dn/aqUsTzGFINpDSZbcTgKUm6Y1KjX9q2b8Onl2puJDtsewU9D0ifhjzhiml+ZiWAJJgg3mY9Ytj0f+1QRTy09Hf6gYrXBCAdRUEDpAIPlHpiPEnbrYjasR0PB5A7NMnxCbAHppa9vUDriXiXGwB4dOyHmc93Eix7R2tc9MXs0qUKDTEtcRTBIuDuFIgSBH07L8ulNz4YRJDNPKtiIPKTsLzHkfPHOlGN/kWPHFFMHFYiVllA0nUQBEX+MTNsPKXEKBpK5pvq1HxDM6mYmNzDEiWJjoB1xas1kEZSAFRgbmBYWPeIt54WZrhVSoFpxKhxLCN5E+UgSfWO90njTqhZYa6K3SzVBVVaanWRdmg9ie8GZPkBHWcMstn08NQsB5a95joTJ6A7ACwHfEfEeCGjTVtMgNcgAECZMj3eo69exti8MPvAAKSebVIdZgMNtjYkWHa2BLBF6B8daHFF1J8ZgCaVrGAJDAQGkGb228uuFfFs6xZnhL7WANid4uLEiSO2N0qkIwYAwQKnLBG5GqbWvM3jfbEjcMBGrxFGwVVg6puDcf8195GEjgSfJjVoSLUIRhpDA/aYixE+6DJPefpg7h/FqK6g2lWAswWZMRJE2ki7eZt0xArg1B7xURMbkRtuOgM26YsT0ZCqEBRoAnUHIK6gduqj0vtiyWJT0wLGpA9L2iUkwVg2J0jYx0IttuNsS0s7LhVZWGxmxNhEaRuN/ge2Jjw409LJI791i07DsRe3TG1BuNm6jzP3rRJiPQYrfh460P8KegbK5VaqgNWpU9RMkAQoHUmb7bza0C2GGUyaU9NNoaAS50l9Qd9X2CCoIMCQBBAm4OOMhladICoVJcEMy6pQiV36btHU3A64TcT4mzvWBpV9TGwBlSFghTYbADcEeWM08MnPhFaElFroGr1ZYm1zjeA6pM/0xmPUK6M9MN47lKNOrSp0qKSxV7pIgkRP3lgT6Te+FvF21NUINNYK6QiwIOqwUQV2Ebzv6QccqVVqyS4IEBmQoWncxFrGOuxvgcMIAgnWILG5AsD1M2+I+OObkim7NLI8k51T1DBr226Cep7YKr59mczPhqBA3iPdhe/eSeu22Ilq8rakAkCSNxqBIjsIHTyxHlM01dnZoOgBisAA3iwVQAJK2iMRR1dBhSTYz4ORUbnQCRY6N4gBVsbk3mCfTDPP8HprSvLAw0AEHaJnqBIvtJ674ESq9Q6JKxIAB5RFtpuZIk9ie2HGY4ijppViV0qs3nlDaTJmPsk+gxkyTlehX+XYr4ZkP3oNJWYgAzrI2IWZIKg9bHsPXjPsVzNRY0mmwE6i0sJgszEAcskGOh6YJoqoKsrqjqNJhiJELGplaOkQIK9emJaSgvm2bwjLe6w1DURrHUSPeAJ2CkxNjYpJphUdBvCjqJqlSEjSSE1FiQPtQQJF+4keeHkVDC+KFgrpEE3EEhiRG9om2luwOKtk8yUKBXDgC4AjewBWSIgza0QNsMMrxnxVCgAhKRhh9sADUSTf3VQEEfagecjljG9DQkix1a7gqrKBGqQRuAYXtIlSxHQQR1IXZyoaYlpCsAFPMQoUFQZC2tNlG0dsLaftC2p6TAFiQhYoCAt7wZ/zW30XwVl85+00oBDEtfpcy0LqYE8u/S3qSmbllqMSSdoIy3EFA8NzCqwFhDBQzAsQNhJ6Sd8HV8qW5lBtBPfblAm5GkzInf1iscUrMkvUSeYkFjJBO6iNt9Q8/U4ufs7RigkyCw1G9+a9zvO2NPhpx19C3qiHhlY+jC3qJ64Z+0rj9mqeg/wC4YITh9wwsBuTFxiLPZY1AVc8p6SNt+2N7di1RT8sNK7H9CdpON8BYnOU7FQS1zN7Ezf8AV8WFeB0wIGuB2JNu3u44p5ClTqCooOsbSRb4RbCRVNsLehZ/awP3VA/8Q/8Ab/TFS4WdhJ3xZf7UHLUKEm/inp/CcVHhrtO5Hy/LF0RJFsqVl0IWq1dSEsAHKiToEWu3uzpHqbTis8QzZJLuwkEfuxHOG1tOuxIUqo391t8O+D1AHIZraWM6iDZWXQI96dRtAPnvhXxFCCzs6BmIDSvMxOnVqGkkrI3mILbBiMc/Nj5ZHBd9jt3FD7IZlan+7ID3CvDc1oVYILRIg3AXeInBwR2BUksDJBFS5U8ypsNOorYdyLQbA0M6lNabgKi6dAiJAbUykR1EQDF4mxONVq4QftFQSNMopLBVAJi5MTYmO0nzxnWdQ/Fl0eiXLZUupIMczFJSfdCspAO+zAfZPQRtJSyf7xgI0qTCwDy6ouyjlYjXAIvLwA18bbNgMAKwBZBGoMoRZYsgtYkCJI7WkAgZQfBpslXSykSOZbvz8wmwBYmwmw62xY8kZK0EWcV4atOgXcAHWvKrDmBFSGPq6kRYcpje3VDP0sxURdKpZAA2xJ3AIF1EAy28+ZBL4syNSQuY8V1AQ6idQBBIIjUCzKLRsxxmc4VSpgJT0a+UkiTJIHvdIJMxIEj4YT5EqTYvF+gvhPDaSupX/EaXkiCBOwK8oBIgT9kzBwXUDwAyg1QCdJJiNxB+0YBWSSTYS32gEqqhJqVIDEgAK2pAmpWiFOowFUBdIAaRtfMhVdmdqmYOhRIVVIGolakP4gKsoGkTp59DdVOLecErGqhpmUphl1My1BoAYWP2WjU9hq5TB2M9oIGVy0amKDQh5CBczZeZn2MsdW8BhfYC5zJ1aklXI8OmzF1LNurMQoC2YorLPMWNRjbbEmRAXU1R2KgAPyuQzvMe9EhSD0Ji5NzhXmjVogRlszpQSdIaGBBA1GAXYc0ROowCZ19Igl5HL0qZpPrMilqO8EnSGAEdbb9/krq5RWTmpkBGW0WKiQRGwNgCoiAonzyqwpmmFeCgPKWJsVF77kNeO3njJLMpdIDkis1kKmOUxF53tvjMd57h7hzzLsNmPYfx4zHfTddGSkDZrh61TrY6nP7wyYXTpWs4JnfRqEDuMR8SzVGogFMhDUBYjSWIZVYAcvuqSwXrGifLEVWsGpimiOyrcQtiTaSbRAgb9MAcQ4C7VSKALpCkQZM6V1T0HMG69scpOL7ZYr9nXFMuku1NwUVtIHULJi1tyGsNsR+x0ftJDFQmjmJ2gMpgx0MRhhl/Z+qtOpUrr9i2okEfEfgcPPZz2SavklqA07AnUwM6TAWmAAegJkiZJv0xY5qUGosuxwtbB/2BQKhSpL/ZA2IARbki5YtPawGFS0RUrBqbaUWBfblVFIE7knr3OGeR4VUrairroSaZRlNiDc2tNomdsMKnAq5BHiU4lDGgxCiCLnr+eMfJQdNqytxpmNTp1fEJURVZZtEwov6w1x0g+WIaNMPVzKEAOYSppB2lhK7wz6aZN7SR3xPkvZ+tSphVrj3tRlDckjbmtABnvPyiTLVaubzppvokwTpmzBha4i0/PCRaUZJSHUtbAeFoBT5ZtqIeJJBAiY2iDbzEbYn4flRSqeK0KqyqqbBhN945bAgHfVHbB2U9nWp0wilpB30Wa8zpDeguegx0/CKp1jxLPAMU+ikPBXxDckQduuBLJC3vQiEzFPFIAO9vVjB28tW47HD7LLy6AbSLQItfaIwHS4E1NtfisVAEr4caioIEkvJgsTMdu2GeUosZ0rM/IH8BjqeE4OLadiyu6OlNLTemtp6b+cAW9cOclxUi0ah1g/UW/VsC0eEz7xknoNvpf8MH5bgCLeYPaTb64veSCCoSGVPiCxNrbjqPXtiKtnkJ95o6Qv54iqZNVBYEWBtf8Ab/AFwMEt+vn+u+JGSfQ0lQW1diCAWiRb6j645LT7ztA6T+WIEQavLp1nBET+hhhTyzi3FnakuXdtXhVjBO8KGSCeuOMjVGF3F8u7V6wAP+NUuP8zYlyfDah+8P154sUqYlaLIjTBkiD0/phlkAniKWAN4MibbR9cQ0OAVFUEq8WIJqLf5DEjZCoLgAidgwkfOAcD5IMnCSLXnsihpONIEow22kESO30xWuE8SosqLOoKC6hhdjBMbnZWYdbFRbDpM8GoHUSD4ZBv5EHbv0x59n6mXVVFFTIBHvtABuYmDJMi3THM8zEp0i6L9jyrXphNBKA+JLAAA6dU+GADe+rab7+c1DiVCjoll1C4ME9dSkXiOXf0iNsU2ohqMx0SWJJALH3pJ+15n54My/s9UcT4YAIuC5G3cAzjLLBCMfykBy9jutxam9F3DFvDzCOOhClrdJB94n4G+OjxSgEJB1ShDEkbjQw0zsDqYgfwqBEQAF4OaWVrIygtV8MCCT7rFjJJtvheOCVjYUhYEi569Jm2I44mv5ElKkmNa/tOGUciagIBvCDU/rO+xOFlLjhZSkSd56gsQTF9oEfHEWRyRR4q5ZSDa+odbjs2HWZr0KYIFOktrqq37T7u8euC4446SsW77Yw4ZxZAFYPqeoyjRqvdAl56aVMkdz1OCaXE0bSbe9MWABI5RI5m3vbZu2KIFOrUCgF4sJHyQ4YLUdmBFQLIuCBG82kDfCS8eCd2T5EWTjGbp+DS1O3+7qMogXPMyw0ErLTqvIEdQcR5UpVoOSwqOl+U36aiJPm4t0OAzXZr1aqnl0iSGsNXlPX6Yhy5RQ2jyv1HpAiL/XExxVqKftBckcZynTDEacwLC3hjsO9PGYgr5ttR/fH4If/HGY76b+yksHgUxcqh828vMjBNOuPshY8ojCXIoHoJWZyAVBMs0T9qw3uMG0VaLaiOlzfzI2/njyk4tN2TlK+gf2tzWjKuT9oQPMnyxLkM8mS4b4NVzBAJKXZWcgtE2iPw88JfawDXQp6llnBK/EXjsL38sd+0ykNTVh+6kNUaSdjZYF/jfcY24tRhFe7ZdGbVDfgeqmhY31wQOvXmMGJM+eLFQ4zl9ADWqC15hu5EW/RxXaeZpuupaqgHsIPyImfXEdTN0xsxY+QJn5Wxm5z5uVFSyzTuhvmOKUm9yWXoWaLie+/wAJ7Xwn4vxllB8OiCO51X89hIkNv5emOqFVXuNML1KiF+ZgYKyWXFWQl5F2KHT8+uLYuP8AYiyOTlpIq+Z9oMxqCJpVjA5UDG/QagcWfhbZzRpqtqcnZpaPJpBH5WGD8twAI2o1WnyhB/03Pzw2RbRMx5n88a3jUkk6Q6T9gOW4dUKxWZWJEQq6VHy3+mDMlw8Ae+I8zAHkBMYhzbMALncfiMQyT3xdGPBUhx4KVMCAVvuZE/PG6eWpDYL88V5tV742jt94j44ayFkqJKkAqJEd4+uBRk73qjysP/LCdazH7R+ZxlSqdpPlf64ZOugVY7XKwZ8Reh27f82Ov2P/AIq7dv8A9YQBm++3zP8ALHZcgTr+uI8j+yUiEexdLUztmPeYtso94kxc4Ooez2XX/eE/8y4WMzH7RPxxNRB7/XE+WX2TiixURTVQmpSIi7DAFagAeVgfSMLqp7HApdgyxq95dp6sP5YS7CNauWVlIIBkEWxUc17Gf/W8DteR89/TFvNNt4PyOFPEq1VGQ01ZpmbEjpbCbfTC0vaNexOROVNbxSpVgoDKO2qZkcu4xZM54TTHhn1PW99wT8O/phbkc4YkqV7g4nq0Kb3UaT26f0xnyxn9JhulSRBX5LikWW+zHpt1Mze0za0nEaZlQDrosYAMS+5m1us+XzxtsuNiI8jP4TGMGWpxBA+OMfyQT3BCcl9CTjftPURGRaCqpmdQLC/+YQT64WcGFLOcoTw2W50U7f6gY+YGLf8As1G0opI8sTI6CygAegw0/JtUo0Vzal2Jx7KUrzqPyEekDG6fs1RXo9v4sORVnr8saLfo4z8pv2LS9CmpwOkdpX0j+QxFV4ME0kOxMgCes2w8+GA86w1Ip82+kD8cafD+SWWKsTLJRg2Ic/w9fEa/0HYYzE2efna/6jGY9Po5H9Rk+xDwbidN0SkCBoAEVOy7GTYYbh3WWCpPQkj8ANsUIZB5vhhl6bLHOfnjhz8dN2mde6LFmczWMGqikdDpDD/qBxJlOLqDdVt2QDCLwmaN2+Z+mH/D/ZOo41OdI6A2Pym3xwP6dPQNvonp8WXV7xPkFnDA6mBsEB6kH6DAlTKU8syrpu19W5sYw3oimYILH1MfhixeHBbkPGDfYMnDKbEE1CxHTp8sM6dPSIFh5Y4FZB0H0xqpnqY/3YPyxaoL0i5JI7axEfW/44KNdtgcLxnqc/4Q+n5YKqZxVE6Owj1+ODxaGsFzGbcsR2Nh8AfzxtazemJErJc6PU7fzxqrmaQ+yZ8v/eIQjOZeY1A46GYfyxA2YXonpc/njSsvVT/qb/ywtBCPHa94xBTzjnqO+N+IgGx+Z/PHfip936f1xCHYzTR0x3+0NG4xH4ifdP6+OM1p90/r44BDVXNnviFMyxPvD5Ymmmfs/r540ugbD9fPEIaqV2A3GBnzL/ewSVQnbEVXQPs4iDRmVztVqaMSCWUE+pAO2Jf2h+p+gxxlKtI8oQDSBbSvmLfLBBKD7A+Q/LEZAYO0f0wHxLiBohGtdoj4E7/DDF84ot4Yv5LjP2sEe6Pp/LAXfRGSZHiVOsnMPmNv13GNPRK9LdxcR64gOb/h/Xyx1T4kVtAjqJt59MV5MUZ+hXFPs4LDuPnjTP6/GMMMu9DMrKGD1AsR6gb+uBMzkmTcW+9H6jGTJglDsyTxvtA61DNsTrWPaccAeWNkgf8ArFQEiUViekfD+eFfH3ZdLIRN1IJiRvIJt5fH5s6NZQdvxwDm6Vao+oCV2AHQDqQfxxp8WXHImXxx840yqVeI1CTIv/npn6jGsPKvDapJMr8Gj6RjMdP+ph/cD+nx/SFK8HeL2n9dcG5bhNIEeK+nygk/IYW8U406HSrXFpBwsfjVUi7m83/lOKMaUl+RWlZ6Tw5spTMI4mOqAn0mLYIPGKWysG8ggH88eYZfibEQZJHofxwQeJlTBAt/Csz8salwSHuiw8WQ1GDPW2mBpUQCZ6Y6yuqJ8YAeY/lM4ry8WYkGRbqVG/lbBS8R1NJKn1UYb8apETZZWy0wTmEHW4P54kpUk/8AvRvRT/JsVn9vgRyxvtjuhxJR9zz3/PAaQ3IswqUgY8VT6L+bY6zGYp+74omR9k2vM7+WEPDeK0dTl0QJ9nf6XnBVHi1Lw/dUPBmdUarx1j/1ih5I2NySDauYESrBuhkx+M4iR3YwuiT3Y+UmwwM9dfD+xrjYEwG+d74CPE1VZK8w+zLb+V8ROL6ZOaLfTyRAksnzI/ljbcLJAgpHqfpbFa4f7Qa11wA2xBLfWTg2j7UdCosY2P54j4X2FTQ5/upj9tLdJP5Y6XhLd1+Z/LC/L+0FNhI0AzH6M+uDsvxwNPuWJ2JO2EfH7GsnbhbdCvzP5YwcLbuonzP5YFPtCAyrC39bdBjeY49pqKkKQ25k26DA/ENk7cJP3l+uNtwk/eX646bikH7MfHAGa9pNIsFPNHXbvv64lxByoNXhJ+8Pkccvwf8AiHyP54FyvtBJhgoHx/PBdXiwEGV+v54icCcrBstwRw7S63Aix6TbfzwRU4Ox+2P9J/PEeY4xABBWxFr9SAevngpeIlttB+f54PKLDYvPAWn/ABR/oP8A5Y7p8GPWoP8AT/8ArBFbiBUSdIHeD+eIf7380+X5nE5RBZh4R/xP+n+uI6nB5/3n/T+ZxI/EmH2lj0GBq3GCu7LPbSPyxOUUSzrhvAqdGCC7EbEtH/bGGxrHy+WEn97MZ5h/pH8xiJuLn79/QenbBeWL7BpDOrl+ot5fr8MQ+H+jhZ/fbEx4nyA/LAef45VUBlmpBggnpB27HbpjHlxQluPZXJR7Hjp6fLGyhFgd+8fLAXCuNUqwkNfqDuPh1+GGDLjPxcXsC+0BHL+X1/rjMGafP6DGYgf9FE/+N+IZLwBfAdTgAAs+r4YzGY1RySvsKSOqXCKgnSQPMdPTEdXhhBhjBgDv9cZjMWKbbork6Oa3DCSNJ2H6640OHEX7ef664zGYdSYGzr9mfb+eOaeRadxOMxmI2I3Yxy/CnIAAAuJv06/XE65FlUSAQo77tY/o+XmcZjMZJTdjo5NGuxVUChFW2128zvviWtkWM8tyBAmLgSZ8pI+Z6WxmMxL2OooCSjUnSLCTcRO99z2H1weKRJmBABtbpMfh9TjMZgzY8YoWpkKhVlCgR3O/SLfC/wD6xJkmZSTNk7fegXv674zGYZO7QzggpMw7bDUY2sLwAAfj6741pLQ5AUafUi879tun9cxmFlroTirGDuQsAfMz0B/HAeowDpA6xa8H+oxmMxWicVdGuKOVpoCAWeG+G+/nYY1RWuygQAet9/Ly9cZjMFOohcUEpQqyD9ki3NJnzPriLJ0MxqZjHb3u0XgeZxvGYnNiuKsnanU0S0nc6dXUeZ9caXLVNIkTJnodItYSfWf0cZjMDkBI4p5WsNQCqL7EzGxI/X8hiQ8KqnooMXMg/SBcj6jGYzEc2BBL8KqFtkChYF7mYJJ5b7RjlOCOdRZlAMjlB6npf8tzjMZgcmOTUuD6ftHzj9f0xlThAAG8dTbvM+d8ZjMTkyqemSZDhqUidKrczIHfpOGVND0xmMwWwxRvVjMZjMV8mGz/2Q==</t>
+  </si>
+  <si>
+    <t>NHÀ THỜ GHỀNH RÁNG</t>
+  </si>
+  <si>
+    <t>Cách trung tâm thành phố Quy Nhơn khoảng 3km về phía Đông Nam, đến khu du lịch Ghềnh Ráng, du khách sẽ thấy đối diện khu mộ thi sĩ Hàn Mặc Tử là nhà thờ Đá nằm sâu dưới chân núi, hướng mặt ra biển cả bao la. Được giao hòa bởi không gian thoáng đãng thơ mộng của rừng núi và phố phường, nhà thờ Đá mang một nét đẹp đặc trưng trong lòng thành phố biển Quy Nhơn. Đây là một điểm đến không thể bỏ qua khi du khách đến tham quan thắng cảnh Ghềnh Ráng – mộ Hàn Mặc Tử - bãi tắm Hoàng hậu. Nhà thờ Đá Ghềnh Ráng có tên đầy đủ là Trung tâm Thánh Thể và Thánh Mẫu Ghềnh Ráng, thuộc giáo phận Quy Nhơn. Theo các tài liệu, nhà thờ Đá được khởi công xây dựng vào ngày 11/02/1963 và khánh thành ngày 15/8/1964, do linh mục Phạm Châu Diên đứng ra xây cất. Sau 40 năm trải qua mưa nắng, gió biển bào mòn, nhà thờ đã có một thời gian xuống cấp, hoang phế. Năm 2005, nhà thờ được tái thiết lại và khánh thành ngày 02/02/2007, thu hút ngày càng nhiều du khách đến tham quan. Do nằm trên triền dốc nên lối đi vào nhà thờ khá quanh co, tuy vậy du khách vô cùng thích thú khi vừa đi vừa ngắm quang cảnh thiên nhiên tươi mát xung quanh. Không gian xanh với một bên là vách núi dày đặc những leo dây trường xanh, dương xỉ, một bên là bờ biển dài cong vút càng hấp dẫn bước chân du khách nhanh hơn để tiến vào khuôn viên của nhà thờ Đá. Đứng trước cổng gỗ đơn sơ, du khách khó tưởng tượng được khung cảnh bên trong vô cùng nên thơ, trữ tình. Qua cổng gỗ, du khách sẽ bị chinh phục và cuốn hút bởi khung cảnh yên bình và không gian thoáng đãng nơi đây. Từ cổng vào nhà thờ có hàng cau, dây trầu, có những cụm đá ong làm nên một không gian thanh thuần, cổ xưa. Trên tường, men theo đường dốc có phù điêu Chúa Giêsu và nhiều tượng Thánh khác, càng tô đậm thêm vẻ thành kính cho nhà thờ Đá. Phía dưới nhà thờ có dòng suối nhỏ, sân trước hang đá có hồ nước trong xanh, bàn thờ dâng lễ với phù điêu cảnh Tiệc ly. Chung quanh sân được tường kín bao bọc có những bức phù điêu điêu khắc các tiểu cảnh về Chúa Giêsu...tất cả tạo nên bầu khí yên bình, ấm cúng. Đến với cảnh đẹp thanh bình của nhà thờ Đá Ghềnh Ráng, du khách không chỉ đắm mình trong khung cảnh xanh mát, mà còn cảm nhận được sự gần gũi và nhẹ nhàng sâu lắng trong bầu không khí thành kính nơi thánh đường tôn nghiêm hòa hợp cùng thiên nhiên “sơn thủy hữu tình”.</t>
+  </si>
+  <si>
+    <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBxMTEhUTExIVFhUWGBoWFxYYFhgbFxgaGBgYGhgdGBgaHSggGBolGxoYIjEhJikrLi4vFx8zODMtNygtLisBCgoKDg0OGxAQGy0mICU1LS0vLS8tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLf/AABEIAMoA+QMBIgACEQEDEQH/xAAcAAACAwEBAQEAAAAAAAAAAAAEBQIDBgEABwj/xABGEAABAgUCAwUEBwYEBgEFAAABAhEAAxIhMQRBBVFhEyJxgZEGMqGxFCNCUsHR8DNicoKS4RVU0vEHFkNTssKzNGNzg6P/xAAZAQADAQEBAAAAAAAAAAAAAAABAgMEAAX/xAAuEQACAgICAgECBAUFAAAAAAAAAQIRAyESMQRBURMiQmFx8CMygbHBBRQzkaH/2gAMAwEAAhEDEQA/ADFEBmYFTg5cMl3KbEJG5inUSgpIomAPapk5dPPYmoNe/gxyaZ6gsEKSCQ/R7nZ396xtiHP+LgoArKViZTSSaTyFsBvxvGDnVxS0TGa5RCkqLF7B8noBewJN4YSZCUlwoli5Buw3vnr/ALwoTNcqSCXyCVG9gQMnbxd9oqRxAv7yknJBs7YtyPO2IOLM8buu/wDw6SvRqdVMSkPk9L/CIKWioJ3IcesI5WtIV3mINwxvySxvsD8IZT9UCXCR3QSLjo149TF/qHN23XWv7/8AZnlgpV+oWqUIrVKED8PmrWolX9vLzg0iPYwZfqw5VRlnHi6KOyHKOdkItaOGLCkOzETEsco9EhACSEocosTLHKIpi1EBoZMqnrQgVKx+jHTqJYKQ/vJChY4VjAiU8OUD98fIwHrVusd0ilQF2vg7eMeb5GacctJmzFji4WxoZIiSZQiUdEbqM1lZkp5RAyRyi4xwx1HFQljlFiZQ5R4CJojqOR4SByj3YjlFyDHSmFsJSJI5RISRyiwCJhMCzipMkcomJA5RYkRYBCNhKxpxyixOnHKLEiLEiJthSK0accon9GHKBtdxaTJIStYqOEuHbmeQszwR9PlffHx/KJOasaj876TUELZTqw7v3rg3y39hGt0HD5i0khiCAskUlKlOQwLOFNi2T4QHqOHy1KrLAlxUFDKTv0d2sNzffTV9mjsk3HdAUALlqgDyUMVbnyMeLDg/vfo0Sv0A6RTO1Tj3S5t4JbLDm/zgzSyETClc2WGfvZa4Z/7D4RFyFO9LBy1jzbqSD+Mc7VU5JpLJDOprgkH3QLKBw+A5N2aO8bkpdf0Z0ughWnQF9mhLkF7vg3y1rU557PAvGROQXoFL02A3D3bYXGNs8q5GrEsipwXPgWyCf9+sEiaqqopsWa5pILUkHFrF+saVODi1XGX9hWnfyWcK1IBcqepnvuzHyfr1hqialXukHwhdI0ssTUMwy4sxJsLb7+cH6XRiWCA5ck36klvjHq+E8iXHTV7MuZR7JGImJkRAx6RnPCJCICJpgBLExakRWmB+IagoMs7FRccw0JOSirY8U26QVNF0fxfgYH4mDUmwDqc+nh0Edk6sLWgMQxeJ8XF0+MeN5M1LLaPRwxax0w8x5MUa7U0hg4JOWHn8IJaPTx5Yz/lMUoSj2dUIg0TMchxSMWJjjRYhMc2cTQIsoiCYuQYk2MitomgR1oslphWw0eCYmEwBxbjMvT0hf2gT4Mwv6/AwBP8AapCZVbCt6QkGoPZyWwL/AAMZ55ox7Y1GhSmF3H+Ny9JLrWComyUjc9TsG+UT4FxQT0ksxGWxzDXOxGcx899ulNrKKypNIUt2YEl/GzJv4xDLnX0+URkgTU8WWZxnlakrU7OpykF2YNtsLRd/zzqf+5+v6oz6J61KpIcZZKQSA23UB9ou7bTf5H9ekYMbdW5UNVmklICikLdsAgKdqSz3LDdzyPjE+IyBMmVFASp0kXdIt3hSCzEsxYYPOBpmmMzuIXMDTAwdKnDuQFbG4HgYiZAS6CpdSTazhxe+DYUnb3olzlwaS+0slTsNWGSEqcU3Hx6Xs5PTpEdMO+oFVrhJO3MMfyML5OsUpYlFb3o7zswculR2cjPPzhnMkISk1k1J7wQwLs+VDF7b/Gy/TlfKPS+Qv4ZZxGUDMWQhbM5qIIU1KaiWvs+WLdBHdBKlzGS67jBbIO3p8MiJaeeHqLWDBPPk5yAzXI6xXIlJbtEBikipLMliVA4LkMRnmL897nFyUnX6fkRppUOdJISLBJBSGZVzkl33uTgxaoRPTSVAB1lQbfPmRb4RJSI9zBqPVGKfYKoRAiCFIitSYvYpS0STEmjwTHHEkQv43/0/E/IQySIW8bHeleKv/WM3lP8AhMtg/nR7hw+sTBvFU4/WxgThwaYmDuLHH62MeHLs9RdEeL7H9YMNFJvCzjCMZ/Qhok2EbfBff9DN5fo40RaLWj1MejZiIpEWCOARaiFbGREJi1AjgWm9x3c3FvHlFMvicgkgTUuM3xvmIyyRXbGSC0pi9KYz3EfaeWgJ7IiY5Lm7Jbn6E+AgCb7ey0qoEsrKQ6yC3wa1/ERnn5EF7GSLP+IOukiQqXWntbd1gTSSCQXFgSE46RhOGJM0oPbISbC7gJdRYOCzfpor9puJdtNXqFIFwAkJBdri5A7wZr33gGfxIzFFYcFgLWSGAuw+0MP/AGjzs2WOS9FEbiRxtGmCgQJiSCFM4+1zd0ghzndiHEYziSu0mKKJZAmq90AAhGAlhi5+B8YjMcpAXYJUCVEkEC7s48Q3hFOv1/ZMoB7MADZr58fGIc5NcfQBhoNPMSszJgoszCkOS4sQCHy5BeKu7y+f5Qn4XxBU1SnHdBF6Ri9iwaPfSR/931TCuLTphdmvl6pcn61BBU4PZnpd2Z7XZm3beDNJodbNJmkFQWXcAOHznk5y+DmEc/V1rKpjpUn7F2LAMHHg7g7w94BNmrRfUkd4KEs3qADXYgh2FsdDFMc4JcZlXFvaFfEuETNHOZaStC+8CL3csXuXqIsC5BN2MOdPJWtNqFM5ACj7rYJIYKvgfFnJa/aCTQUGUJhSSmpTMzm75G23pCuVq0kvJBQm3dUay5uSD7zbMW2zeHyrEk2nYFKT7LJ2gd70q/dqIUXZw2/7v7vg9nBp8okFnDC4N/Ag7G7xKdNWEhVQJ94pe12pIZuXjE+yllAU/eOSEtd8ObqsMjlGfHkgoqSe18jtGvKbA4tCHW8USVKQklrpJY9HAts+fzgng2rBQiXMVU4KTYNY2drO9vMRn9YU9uqpeS43FLWZT4BUbA42EezPynPHFw9mOOKpNMf6SYwpJtsWsfD/AHMEFMKZyqbAglObA5AvcMbXfpZ4Y6CcVMGFhzF+oY3HpGrx834WJOHs6Ux4CCCiPBEbbIlaBCzjnvyv5v8A1h0lMJ+OD62UOivmIy+U/wCGy3j/APIiOh/ao8YO41gQJoU/Wp6GDONAsLR40uz1F0S4se4PKD9P7qT0HygXiIeWnwH4QTpR3E/wj5CNfg9szeX0i4mPR1KYkExvsxEUiJTCQlRSHIBIHMgWi1CBCXjvGFI0ip0nILVZa7OARfxNh1xE8k0kPFHzJGuKitSppqKiSkFSAHUCTuFfaDW88Aifq0oNEuWxUB2hJJFwHYcrr9RfcgjU3WpJQLd9ZU57wU4TaxNrW928LtPqzMU1mduoAGCfTHKPDmrRoof6vUqVI7ndIZg4DXIVffnfweM1qNSuWlKUA1KUVKLgl7G5x5R7XzlAuFFgAGu55B93IEAJ1Sip2ukCzZAPV8wsYugpDCXqpiwHA7rubFjbJ2D/ADij6avDhri4Ja7W6B8dIEmzV3wxNXQXJtf4x1U0kEn/AHyXh1Afig/VaoAKSCWYuUkPexBA8LtbEKl6k+6n3TvvtlornIOWIFntjzHOOBYBH6aGUaOUaGms1fdCJbC3Lcu43u/zin6Ovmr1P5QNJmlKwp+d3x4ct93gntZXP/z/ANUCmgVRpeJaOYCspCVp94qBFQAHeKxgXt1bDwdw7VrEtMskOWpBAYEkl264ZtvUqbxUrKwe4lJFaSz0gsagj3x3R+78I9I06FSiumpbd0UEq6u4ZmILgbHpGfMkooe2xvpOFAUTZjFVKhSkApcP0FyXvttHpuhCHMlATfvAMwLDHQHkISyuJTZbgpYEVM5FvAO1xy5wRL4yoEAAsTn7YYg2vluYa94xuOSx9B0haSlpndW5DXGLZItgevhFWtWmkG6WABOAl7q6MAD4/CKFagzk3l3Ci+Ak4uHAqLAcwGHnHREJFJwzuc3wb+63Mb2hXGjmeUpaV0uQVOxBdJI29SMtB3DdQUzUzCaiAQHLgg7DHP5P1HTKCwtJSpJGGBwzulyxJsb55bRxCVIISpNnJqwRZ6QFEGrduuTDwyyh/KxWkzZ8P1sojswwYAPZiwHO/rygsaZIwB083OfM+sYSVNUpQKVZaxNQLgjbBLP6xrOG69CEollyedtz0O2Lco9vw/P+o6mqr2ZMuGtoOUiI0wUpEQKI9hSMpS0JOM/tpfRJPxMaKiM/xj/6gDkgfMmM/ky+wt46+85w39qPGDuMOW8YD4Zaan9bGDuMnBbePLfZ6a6LNYD2afAfIQTov2afARVPH1Sf4R8ov4d+yT5/MxfxHU2iHlr7UyOr1aJQqWWF/gH/AAj55xb2tnqUQl0yySbZYWudg12fnzjTe23BzNlhaQolJJLOVAEN3Uk0+L84+c63RoKQRM8gxNyQx2NuXOH8rJNfoZ8UY9s3CfbADRg1JM0iixdmHvKe3rGWVxxPYzEhSiVBioqsz7J6sfXpCCdpiAoEvd82tcZ2z6xUJYB7ySktzByLZz4CMk8sprsooJHPowVh07l35922x/Pxi6RqEhkJuDgjD7k5u4zAHEJ1xUbXLg/IdLfq8Vz9S7UWpCacE2AGWvd4lxtDU2FanWBJpACxdyrlsBbZuuYWoWxVgknNuuOWflEZKCpYSSHJZye7c7kbesX6nS9kooJdQDqAfuHltcBncBiSCLRRKh0qLdJxdSJcyWG7495nUlyHKeTgU/zQBLXZRPTxz/f4RLR6MqqULgbuAH5F+kHfQZRsldzgbdbfjBckFtICcqYFTDYF/LziMqWHslydmd35DnDLT8ORQlXaJJchu9foSwpv+fjdJpV3CWIuQliLN9oh+WG59YDlQrlQsmyyAHGX5Z3bnEGP3PgIOn6wCkJ9xJbofN73DW9Y5/iQ/eheT+DuX5D1DoWpCgHIIulyl2qNxYlII840ulJmy0dylayAkJKSC1Qp7OzJwp7P0s6Ot0lU1LEGgEFQUx5pxsbW3gvRKQhSlFaUgpFKiLspDKKSzKIuwO/m88ErdS2GzRz+EJSlVa5Z7OxSEKPeLt3UF7kbPg9YDTw1LBJrSE94hqQaVfaF2DVXcbWgXUIVNmS1SwF4Ki7Ll3Npib0hyHId23u76fwdZSVhkrahSFrdJUohSrFu8lLBsmo4tFpePbuOv8i2/Yu4otOmUTLQFEpdSglRNQIArL2SxNg5FvvAxnkahC1CZOWlPNKQXBSAxSHUQFbi4uT1inj+smrKUomFT1d0H9mmw7yE2ANTB7mnoYuXw4KQhKLKls1aqVqYZCVsDYZa7F7wjxQt0UX5h412Ck1OkkjwdQaok3IZjy33IQszS5CkpD1A1X3SEti+WZny5EZAFlAB6uRfN9wpicw80EyYclmTVcliE873Jv4uWjDPEohoZTGlKUQQSGqqSTzulg2xLvt6vOGyCAietFKTd6fvOxD8yXbG7RmOxmEVuVXa7ObGknbnuNh4/TfZviEibKRJoopSlpaylSSM2O7EEsWLNaL+NhjKVt7Em2kE6KVMY9ox5HduoIBFud3eLzKgGZXpWUVGZIsHZ1pDq2Au3TOLWBvVxFKJpQoukp7RBAckFmA86o9mOWlsxvG29FkxIAc4H69YyWr1ImagqBwmm2LE775z+EM+L8TWvuplqI+6CPDvKNvIP4wl09VZqQEmn3Q9ht5xLJm56Rpw4eG32G8N/aj9bGDeMq7sA6EfWD9bGC+L3TEGtmhPQStf1Kb/AGE/IQXwVQVJSxuHcfzG/wARCpK/qk/wj5QVwDUKEsPKqSCplp94XvmxziBGTg+SDKCmuLIe1HE5UmXTMlGaF+8gM1O7v8t2j5NxviqFrUNOFJQReWaQEgM9xtYdcGPpv/ELUhOkKwKmUO7hTkFJcEEtSSbPjLWj4frFFalFIazEB2wBuS4s94rlzcujLDE49hKeJ7MeVm8rvFGp1YIBT4Enlt+s3gKVKIBJdumN7Hnv6RFKKy9kgbAEmM9IpRbqgaqK3S4ch79b9flHJSgDTzs97foRNBBPdNTevpFUxYBJ8hjLNHWcEGcAlKkO6DdTC3eBF3NR6t0w0D6zVhZKqQCbmkW9NvzjqzSAjzLc4n9DBSFWv/F5eO8NZx7SImBLE0oer+KoDPkBtFhnFgAAkO5Uwe3jd/PaKnZO13BPyI9YhLTcEM4Y3xiFZ1DbQ0MovgkJcNgAl+WTmAJUhQWoKSXUAASQmyjYubAEbm3hBGilKWzG4Zy5AbHe5u5HUPDnSyqHWSFdSxSnm3R7MeXlE3JRFbSE0nhyirs1pVUxFwXS3LZoL7FH3vjDPXcQdKaiS4e/N08jgjY9L7wM6v8Au/8Ah+cJzkxOTHOsCClyq+4SlSgWKr2YYPMxTJKRdSmOB3VFV/OnfnF+ukJlkrBYh3YvUAbkXYXP6xFEyQFBJszOcPa1xy/OM6kq0aHJfAQviXZy6KCq4NY7p7uRk28AIoVx5TLUAUlQYtQoLboQkJsAHAOMWiczT1yylg/iRyYMLUxndZpVyyEliFWe1vDnmL48zaqxbGmn4ioJKQoJKySq6hewF/tEBKR4CFs+fNUabhibsxZ9yA+3z6xZ2aCAVG7OQDYePU3YQZwuagqS4IRyIszEXv438GjpT9ndgGiWUzEJAOQCDUc2uBkdAeXKNZwab2iFJYrmLsCq3vME22A/OE+q4Glc9K+0aVLIVMU3eQlJSWtlRBAAySrzN+l14Utc0EBS6qEkvSFEsEgYZNnbbxgSqUdjdAs2VNlGhScmyi7WIOTbkCQ48jD3h3HhMdGplBmpE1BaYlksChzSpiAoAuC1r2Kzt6lNMUVKa7Uk26m5LfhFieEJaXME2oBTrlUErATdgWAYpBBIwT1eGi1ehOxzqOLKlyFyRqCtCySEqSQq5BukvU53e3g8B8O4tOCgkgGkMkqJKAE4ThnB2sHEZzis9aJoplKElV5faKCyRYPUDbvbG4e8NNBqLJYVMHNgN8tyLtvHZG0Ho2K9WSlJXPmlSxUJctICmAvZO3V94NT7PTlJCkqmSyQ5uhSsYJW7X+ULfZzUSFlZrXKmEslJVYhr92lgAcBzYQ4HtM4Se0Z0vakgH+kln3iiyJK2yi2T4bwOfLU61lfKqgNY/dznflBus4fNWGpT/V/aLRrR/mpfnMlfgI4vXp/zUof/ALJf4xVSGaFC+Bali05Q5DuW5AChi3X1gnR8JWlJdakHLoWR8MQUden/ADcrx7SXEFahCrdulf8AAsEh+dG3jHHCL2l4DqJ4SO3KwklhMwHDOGBqVgX5mMjpvZpUqaoz0EppNJSHDhgCrBbBzH0chNQIWslxYrW3mDCv2nmASiS9LiqkOaXuwY7X8o5xSVis+Z8U0qO1pDlALpcNULEFuo2Px3z2tWElSUggbAm/yh8tphIvn92ql7k7E2Pw6GBdT7Mz1JVMlitCcqcAJ2Fz4j1iUeyYjl6lTsCoeBYekdUCpjlnNvziUnS2uC58Q36sYb8FCAhaigKIYB3diCCc46NDyaSs60Iq3uS7Bvh8v7R6tZAGyb3Bx16RfMltMAQgpLBg5JcpYl7M4L8r8oYJlplpBFzzztkfC8c2gNpENPolFQKrpy35g4/WN4zz2ZISkM3MO7B3Y3z/AGjkvXMFNZxbk9wwfdvlA0xa1Ck3INj8IXYFY54PNZBABS7l/vOCSTsBcfoQznpCpau+N2vc23SD4gDPOM5P1yywFiLHNm5kNd38Iv0kxaU/aDKBCr3BCgz5Acj4xOULdiOG7OaPvtWcADJskfO23hF/0Qcj8f8AVAw7qwVBJG4L2G9i4bPnzh1/iGm5H+g/645troDsa8Z4jSAEhJKgTSS7ehx57QoVrELCSEqSoAMB7pI2bZwXGc+mkl8Pl1KUsVAo75Z9yQGO4ZnOYQ8Q4WuQCpUpqiGUh0pILuQPeSG8vlGfEopUW0MJMmY9qSgiwBuk2J38784lP0QmAJWPQsWILG2BFfBCJyJ03tAlSGSmWWYuAALgFywbLkYfJE5QSL0lIUQCxBOSRcfpoR6ZzQu1fBUJBJWaAHZnVj9Y5xHSpl0GkkgkpBuLg3serjzhqaD7irncOeXXPTeFHE5zEggJBBIawJvSepuX8oaLctMHZ7WTE3l/eZSkg92oB0l8FoXSp5qJS9RcHNPTzze2TAs6Wu7l6jUHN3JOATfb4RFUxAUCDUUgEhQNJ22IjRGNIDGqdGE98zkAgB++HBJ/W8em8VpJQqYskKABfIZL4OB1B8LOOTpElFyZRqFylyjlYjm/wgOZIkJKAlalAl1VJYpZwwSCWD8/7wYr5OQdxJRITLrXfvAkmm9yr+lO2WEX6J0ICyQpRUEoD/ZYPYZZ2L+sI9dxVlpSll0igKD704O+MNZzzsbqjXNlyzZHuhANmyAPLaC4trYd0O1zKS6gQVfZLPcfeBOz2LltoGQKUUoCXJqIL91wOtwbbEB8PC2XqlqMxYLCsy0izWufOz+QjyNStNChepzzJAwX8L9Q0JwO2HS5ExQV2ikVCwYFw/ukn7VzCtaNSFBISk1EJChi/lDjSaoKE1wKkC1yXu5vy384ZokJC5anPeUi1mJJcFtsfGHjaKRbTX5mRXrChSkLIqSSk+ItDr2d9qkaev6pM0qa5UQzPawPOEvHeGVauf1mGB+MykyUaYgNVJBUwyoZJ9YtRVvs+lcG9rDqZnZp06UAAqK6yaWwwKWJJb48oYcVlKnS1SzMSyv3b9G734R8o4N7RokAgyUrJLuSoHoLbfnDmX7cy1d06bNmE5behQ0N0hHTHK/Z9aQQFpJP2invJ8Nhe+N1c4YaCYZaygy0KlzGBBLgX2SpJS2A3QOS0IpftDLXYSJv8swn/wBYnqjSErKZyCbpdSC7eF/OEdIDiuxT7VaUVrXLRQBW7kM4BLJFRJJvnkwFoSaCUkqJPeASLJDEEkXLs4z8Yv4jMWtSlLUQMgA3yMBreXOPcD06CSqq9QASbYBJFwQdvQ84Df27Itqi3WzQLBSUuoFSGDqDKY1ByBkM7d4QAjUKIJuSzPsHdj/br0hjqZRVUmk2ewYCz0kkHpjrC4zCgBKnANwftE7fgxxaAnaBHaCOFcNVPPZy0lcxRHlvlvH0O0Dz9DMQEqKVhwCl0kPdrebi3KNTwrUIkyAVTZaaaiiYO9TMKbJIlmupbJV3TSCnvYYZ7iftBN1CmmElN2RUWSCoqOLDOQBYQ9FKJyCpKgpQFkuwFg3d2fez84LUorlgAmoioAC2LFzhg/x8wqZkxTCoywye6rAYkgJJsHD7M/WL0LUhQ7hJuAkNULW8/XGIlJE5IhKFSaJigGCiCSHBD/ZZ7naLPo8z70r1T/ph37McBlTlVTytJWWFLlJOVVmkkBmAZrmPpf8Aydw//Iaf+tcNGvTGSPn/ABHjqimYTSgIKZaKXeotsQKSzkghmAZzcC8V1BVKMxSwe1FVFVmWSRbmGfn3RhyIHncGExImImVKWpVIYsAikgF/dKqhz+MFo4fJRLWozQtUshJb3anaz2pAq2v03yfbSObVHvZ+Zp0oKgCpSyU01kJYJLFg1JBcub2BESlzWSy7uSp7MGBHycRnESkhLAMVgHLqF8gtjuwdKCuyOVOGu5NjcjkDmHnBd2M4j+TNCVBlODszgCwODlvl4Qh9rJMxSnCnR7zjbNhztt4wx0CAhIZQqI8fe5eFh5wNq57LWkgKTQDv3VVDJ6uT/LC4lUwVTA9KiZQruOgopCifcILlVIDqPvBuvQGEplJAusu5sA5G9mJb1jXEjsFu24AcMCA7EeafWMulctMgpF5inqJ2vt5fMxraoLO6fVolByoLsyUJe7KBBmE4O7B4FRriubUWDm2wANrDo/wgEEC5gzhmiqZbWKghO7qLD8fUiC4pbOpIaa/TIVMCgqWknvF1ML+LXfl6wNqEqkLlrDlhU4s4vhXgfQxPW6J5/ZDZIKjuHGD1vjrAZ11Ss2wHwALD4QsVYIjGfx2oFNDEmoGx75e6qs2YNi0XaWeTQpar9m4cDlhgzeHQQjnpDPUDdtuvWCtRMIEr+BJMFwS6KRhcWaf2dFaVEkFlUv5D15+cO51hLb78trN9ofh84zvsWT2czH7Ty91JjQcRSQlDbKRsPvA/gPWGgl9xSUEnH9+wDXSwZ8y2VF/P9fGEPtZJeXpeiFj0UmNTNS81ZffZClPYcjCP2mDypB5GaP8A+o5wFJUik8bTlf72ZNMiCJEkOHxv4ZLRGXJYhXKZT+toYSZJKtrmnbkQMeEPZDiPeEa6RhM+fkWWZZFLgHuqSb+B/ONRxTg6VyyEUsEkpUSRSzkk0hjd8NtHy7h+nCSVEg0jHNhdv1vGi4ZxxfuhRDgpY3DHYPceXOMuSEn0wXa+4nN9kphT3VpJzYKuLfa3ycA4wcwCvTiW6Vgkp2LPhwSCbHG3PfDUcbmJSooCAzVCk7Ol3CxbJY9G5Qll6tU9VS1JKg5YAgi2Ms2LmOSyfi6JZIpIjNlCnuoSoAtURUAAzJf3vlC/XoTSpRFKnTSCQbixDDoXvy6wXM15CSEC6SVVJdhlwp98l+kUo+tVWtDnb94htzc7ZeKLWxY62K5SzW4NyGLJ+9sA2Xtbyiywe1Rw5cEE9BuOvOGk1kqBCEO/pyNQ326M4iyfoAplJKXOQCCSom1yc355h+a9jqaF+n1CpZdJIfPzB5HY3h1wHjoRPCpktKgWFxdnBf1AvtCjiATKsQ7FrG3n5R6VJdNaKiHuHcpzy2cC+0CUU0FxPqGv0qlGqWkA1OABZLlgQ+QATu7FUVfSldf6l/6Izyfa6ZQAlLFNiomxt6gtdv7xX/zjO++n0P5x56x5gNlmtQEKndlUky2BFilSi6SkpUCFJaryV0MBTdIgJrllQChVQXJSqohr3ewN3zB/CZiQipSbrS4dXeK1KIBvzffk8HI4clgtSqAVKUKb1iltvdAAPVyYrG06YVGnsT6CQior91ASxAN7lnfYN8jA30hSJhQSaUg03uyg6dhzBxvDqdpuwlLUC6lmlIHMgAk8gL5HIQmkJKQuhIUghgfvXBJfAHd8fnFVT2VUL2WSFgKAWs1EVEPbNm2F3P8AKIL0k1MwqBDVFicpIFrWdyGt0hZI4OozkJW9U0kCvu3L03LZsAWZ4Yz9AuWUSU0ocqKystQhIQtS1HIpBHqG5QsuN1exZRYDx2ZNAFVgahSGwRn4H4Rm5syphgX8IdqnqQFpmLWQqWoIqABIOCU5AJdj45hIrRzSfcVa+OnhGiDdbAU9i5AfJAtDDizo7OWHASlx+DHpeKNDJIWH5E7HYxSpROSS1h0D7dIZ9g9jX2e1YSJoKO8UrmVvdISgnG9z8TC2VLcYFvGDuGESpMyZ9pRElPmKlW8A3mIG1Si1w2I5dugtaIy5B2AJ8RiCOJt3G2QkHoeULVqYPDDXrQCmlmCQPPeOd2h8d0zTew6Xkr//AC/+iIe8QPd808rBx0fYwi9iy8hYD3nbfwI5G0OeJgmXcfdPM2vuOvOOh+L9+imTuH6f5ZwzGmLvgg+qRAXENOmZLRLqFQUoglgBWp7vjKQ/jE9QT2i+6o3GB+6OkAyyu5KV0ucpOLnlYZc8ozJNJNFvMnJXQrn8NKSXUr3sAWJF3bwgjTkJKb/aBw32h/eLeKawAi1SQKWLuGDi3JiPk1oU63VJKXRa4v8A22jRGVowqbZDUTHUUkOxLFODz/XSOykAFySLi+w6nf0vCyZNJDOfCOyVn0wP9usGjrY6WpYKghTku+bgXwz9cYPlAGnFCiSkXTnBBvcbjrEUqJNWC92JB5/lFtTuMnx9Y6rA9hkycmgkIIFwWVcsDcn7Q7xtC7SFlilTWZ1Gxs7Ww8OUzUoTL+rSZdILlCXKsLKVG/aVJU3QDZou0nAxUtc3vSky1rTMCkpqLApN32N3wUmEVUBLQEdWpLJSgBRYkqBIAOCHOB8j0gqQo2NNJBdSkDulxZi7pYtAqtOgTLDutU5wykgj/wAmtziyeodoAlKQawgA2GAGLvZ2/CEpWIo7C+JaZCzcFYIuQqpiBSVOclmOARfkxUez6ASZSsEkO7MR123jWcTEtCEgSwHZzZyCwIFOTYHGT1jJGZKRNKkLJCitRBSAzqUwD5s140PWmWVlyJaa5gWpISHDhLuX7trWs+LP5xV9BT99Px/0xZxABTrSlRBJJ7pYd5i/pytzMJO0R19YnTfQrTTN1K1KgtSFISAC9JTlVVgerEwz0OslqC1LqQmUyUJKiymLpZz8Aw7oED62UmY4ruFJW4Fu6O6Msxcv4wu1EtdaksSXu1gW3PgT8IyJp9BjF+uizievSoFSSXUspc2dCk1Lb+ZoDTPdNLMGYNY3DAfGPTNOqlmdtjZN7WUTbYfzQZw10HuqKcMGFWcJdy/6aH4/BSKfoOVr0mUdPOktSqyu0+tSRgiWpykWALBI5wXxbVhEqUJywVTEdqSqo1pBNFVKTs5Z/eLtZMTVwghLqUGJJpcFSlOQlApypR94iwY5Z41nBpcmafrZaFqT9UkrSlRAQE2DvT7w8XjMuDyJFpJu2fJDwtbHUSyhSCpnEwFST3rFK2WDu5F3yY3+k9iRI0eonatlz0IWuXStbS6ZZpDghyTkM2140WqTp0LKE6SSWZ/q0C5u3u+EOdLRMloFI7Mt3CBSKTinFiPhHoca7I8Uz4JOlKUQRQFMzsS5PMDp84XTuEzh9l/A/mY0mj0QXNXMZkqUpQHui5cgC12/KLdbPAoCVJ5Ev13NrN44gRFjESL4WsypQCWACllyA6lFmDm7BKfWJDQEzJfaIT2e7rQcA8lObtGhKwAgVD3Qk+IAcevy9VfG5olirvFTsLjru3WHhQ8l8Djg8iSiqZJlhIpKStJYgEpPMvtZmhjL1allkpmLUMBICiwcpekAs/N36wq9jVpVIW4YLUxewyE7bd0/DrG19iwjtlKQbEKLD3RdAtyHLwguVHJCUo1BW/YTykJYChTvSoYxufSNrN0Al6SbRXMUtLgEKKnYJASk94D8ycRZqeKqCyEUlI5g3O+DiCeFcR7UGzKSz8ruzekHYaR82laopQAK3SEi7kVJY/ZIBscZF+UCTNYAhMs1BZpGDdjdw93BYk841kuRLUhiAAbXTtvk2vzzAnEtLJIBKaSlQIIDA3KR1N89Y5SFaMJqpImBQoSHSW7rtbN/F/LaMuvTK7ycsWs123AjR65BlTJqHYDutyBSkuPIiKJHD0qU4UCc3BZtoVKhVHYol6A70+b89oYaT2fnTqxIlqmKQAWQDZzuT4HaD9JpllTZD2saXfdz8Y2n/D5K5WonOk96UFAE2NFTgHY3x1g2roLijIcK9idT2qEz9PPTLJJWpARWAzOkEndtjGv/AOKHCn0mnGnlkjTA93CkyUyw5vlqEuzxqNTxaYoWFIB2FR6XP5fOF+s4z20tUlaO/MSpCSlzlJDhBJyHxzaGaaFpI+XzePDUaeRJEmWlUohlBgsgCk7OQ5qObpi5KyNNOSSbIU9n+2XbxvCLTSu4ARSSzuOvrDuVNFSkkVBdqSoMxZ/jeIT7Eb2R41Ok6lGlTLlIkTO8ilIIEwMmgKILXZgTzALC4XSXTNSZktTJZyXSUG1KzbYh72IEFaKSlU6uc5AnJSQksaQVklJH8I/qjS8akIXNUvSyit5dSkkgqrqLAfaUndtrjcCKckWoF12lCkqVOKQagpKwR3CzY5Hx+1GclIlCtKmKkqdK3PeAuC+Ac5iX0KcCXQUH7TA0g9AMekVzz2ZBsqY+SksnnY3Jezta/SGbTFs2GlE9SQFMEqCu8hgogAFLhW5UbcqeRhZ/hut+9qP65EX+zesKkOpTlI++QSfBrYb1hv8A4oPup/pH+mMk8vGVVYk5x6Yq0R7wLDuEhR2t3RbclhE+1IdVTt+LgCyuh9YgqXMZVCLnYOSCeYAuYlJ4DqVsOzYZdRA59X+EdDG4mlpRVRdlitSQjLkkb/Lbn5RCTq5pIIW2E5QN9nEMpPsnMVZUxPNkhSj+EN9F7DpBCj2htuoJHoA/SHimuxEjP6PVqJUtlL7L7qXSCCwYhg1s2x66fgeoTLce8VNMTmygAGfbHiXPWBpvAiF5lgBz7gLDJPMnAsOUUaXS1VLrIKUky1MA4UxIsXY38SYyZJKMrRX7qDVTbGtXeJKt8nnsI0ulXTISRkSnHjS/zhTK0ZITWsqsblIfABcm55XvDnT6BFIKnV4m3oI248jkt9i8KPjiuGLQKFpAU3O9wPQ9WihEkh0qsTgkAs2MjHj5YjSe0EiZO4hPlyaRQQwNgwQgHbmDCSdLUmeyjcd0tthL2OP7c4R6si9FWkNZ7ywFIDEF8AD3RVkgcuUKdZpJ85TU0i5cslIx5crCNhOmEpLpTYsksdhazO5JPpFiCVB1S/ddy6bnZgThni6hQ96oWcHT2ei7MFPaBROQdze3MExov+GU5R1KwQP2ai4Lg96S3oSsQENWhLhSS5SCqwIDZCab373XGYb8F41KlLKyhV5f2U3AJSrBYswzBa9nJbHvZq+6q/QwXwBCkqWClQBYuUkYJ/P4QFJ9r5JD0zQP4U7noqPD2005LJExRu4CQGZs1Ec4PIajOSuILqX2sulAUACQcXclsHdoR8Q4lNUoEBAIWSAVWPKwziNNqdUlcqspKS77qsQOQ5MPx3hVN1CGFRxkkN6WESxffHegSYv1UszDNUrswZiQxpqUCEJGRgWV/aEZSpIZna1gT1tGo1WvQpJZRIuAB1cfrwhJJ0ymLgF7WC8ZveHaphWyiWSLglxhgx9WjS+yU4pWlc1ZCS7khQJdxtZvMRnDIKXNL+CVcvn+UbP2ab6OjusDVb+dQ38IDgm7OQz1xa8oGYk3TSAX6E8/yj3s7Keepc6UE0p7hPul2wDgi+efSGvBkIoalLBRGBvf8YPmIlD7CPQRS+QksdHxDW+z+qROWlEg01qoukOkLLECpyGbbeO6bSKRSZ8pUrINaVJuCSC6mcGPrOq0spRehPoIHOhCfcUpPgbQrghfp/B8nSUkTZbCpKu2TfqAp2uXFJ8jETxNclZoVSCl2fvJBpIEske8C9yzggPH0fWcHCjUqVJmFmqKAFtyrSyvjCqfwLTkuqRMl2AdCyxYMHCgSbdYHEPGSMiriXaCormqWb1AuXFzULA3ZsNe5i2XrC7rU4N7pYW+y4H47AQ51Ps/JJJlz6CzCuWW86agR4jliF8z2d1SQ6AjUF7CXNQ4HNlMSWA2GekCUX6ROX6F06ZLpeWHWobEuQLs3Jg/l6re2XzHqn84r1GmnyQSvTzJfN0X55xY9dop/wAYP/dV/Sn84zuDu2Q4tn3OXwrmW/hDQVK4dLH2X8b/ANoJiuaceMX7PQLEgCwAHQflHpqSRy6n8oJSkAWDR5t4dQQrkLEcIlqqqKlBQY5SCDfa/wAYVp0gSopD93uk2+8o/IiNQuM7rD9fM/iT/wDGiI5cUNNIeEmVzD3m5Act35eEOJIsP1vCVfv/ANMNJ57iesLHTZV7SPlLq+namc5LzpiU0tgLOQodMiO6vS1rJApIS6lLUaiD3BbGacQmmKP1pf8A6qv/ACi/QLJuST3lC52tbwhrticE0MpKFgEPV1zv5RdLlLxUhhzHWLtILg+HzEdmmH5hWGyaZMx7FBGcHm8Tl6GqoqXSaWFJF87ZxCqfNUBZRHgTDDgiyRcnI/EQ3KxXjoPm6aWlJuT7tOXYJ33PeCj5wv0+lQlSgEkVFyd2Bvd7hrQw+9+tjFEz3k+B+ccna2K47KVSPquzSQzqL/aY48Mefk0LpvDrvWX5A2byVB2mQHVYe8dusT7JP3RvsIHJRHjicvYF9HUf+o3jeDZCaU95SSebJFvIx6YIpIgfUsp/tq9k1rRu3whjwvVIpCAQ92Gxu9jzv8RCJQhN7RLIlggkEKBBBYguMHaGTJyx8T6lw+a1Q5KB9QPyhhNmHnGb4GslBck2TnzjRTRBgLNAq1dflEAf0PyMemRDnDiku0/WD6GIkiIGOINoBxGbpUKykQHN4Og4cQan3m2aJwKQbFX0WegfVzVeFR+WIh2ms+8PRH+mHBiMG5fIKj8H/9k=</t>
+  </si>
+  <si>
+    <t>BƠI_LỘI CHỤP_ẢNH LẶN BIỂN ĐÁ ĐẸP HOANG_SƠ NHÀ_HÀNG GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI BÌNH_MINH HOÀNG_HÔN DU_LỊCH ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>BƠI_LỘI CHỤP_ẢNH LẶN BIỂN ĐÁ SAN_HÔ ĐẸP HOANG_SƠ NHÀ_HÀNG GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI BÌNH_MINH HOÀNG_HÔN DU_LỊCH LÀNG_CHÀI ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ BIỂN ĐÁ ĐẸP HÙNG_VĨ HOANG_SƠ NHÀ_HÀNG GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI BÌNH_MINH HOÀNG_HÔN DU_LỊCH ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CẮM_TRẠI ĐI_BỘ CHỤP_ẢNH BIỂN ĐÁ BÃI_CỎ ĐẸP HOANG_SƠ HÙNG_VĨ NHÀ_HÀNG CÀ_PHÊ GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI CUỐI_TUẦN DU_LỊCH ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>ĐI_BỘ CHỤP_ẢNH NÚI PHONG_CẢNH ĐẸP HÙNG_VĨ HOANG_SƠ TÂM_LINH LỊCH_SỬ GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI DU_LỊCH CHÙA DI_TÍCH ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>BƠI_LỘI CHỤP_ẢNH LẶN BIỂN ĐI_BỘ BIỂN ĐÁ SAN_HÔ ĐẸP HOANG_SƠ HÙNG_VĨ NHÀ_HÀNG GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI BÌNH_MINH HOÀNG_HÔN DU_LỊCH LÀNG_CHÀI ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>ĐI_BỘ CHỤP_ẢNH PHONG_CẢNH ĐẸP CỔ_XƯA TÂM_LINH LỊCH_SỬ GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI DU_LỊCH CHÙA ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐÁ BIỂN ĐẸP HOANG_SƠ BẠN_BÈ CẶP_ĐÔI GIA_ĐÌNH BÌNH_MINH HOÀNG_HÔN ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐẸP HOANG_SƠ LỊCH_SỬ TÂM_LINH GIA_ĐÌNH CẶP_ĐÔI ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐẸP LỊCH_SỬ TÂM_LINH GIA_ĐÌNH CẶP_ĐÔI ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐẸP HOANG_SƠ LỊCH_SỬ TÂM_LINH GIA_ĐÌNH CỘNG_ĐỒNG ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐẸP LỊCH_SỬ KIẾN_TRÚC GIA_ĐÌNH CẶP_ĐÔI ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐẸP LỊCH_SỬ KIẾN_TRÚC TÂM_LINH GIA_ĐÌNH CẶP_ĐÔI ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐẸP LỊCH_SỬ KIẾN_TRÚC TÂM_LINH GIA_ĐÌNH CỘNG_ĐỒNG ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐẸP LỊCH_SỬ SỰ_KIỆN GIA_ĐÌNH CỘNG_ĐỒNG ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐẸP CÀ_PHÊ BẠN_BÈ CẶP_ĐÔI GIA_ĐÌNH HOÀNG_HÔN ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐẸP THƯ_GIÃN GIA_ĐÌNH CẶP_ĐÔI BẠN_BÈ ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ CÁT ĐẸP HOANG_SƠ MẠO_HIỂM BẠN_BÈ CẶP_ĐÔI GIA_ĐÌNH BÌNH_MINH HOÀNG_HÔN ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐẸP HOẠT_ĐỘNG GIA_ĐÌNH TRẺ_EM CỘNG_ĐỒNG ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐẸP HOẠT_ĐỘNG NGHỈ_DƯỠNG RESORT GIA_ĐÌNH CẶP_ĐÔI BẠN_BÈ KHÁCH_SẠN</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐẸP KIẾN_TRÚC BÌNH_MINH HOÀNG_HÔN ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐẸP LỊCH_SỬ TÂM_LINH GIA_ĐÌNH CỘNG_ĐỒNG ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐẸP ĐỘC_ĐÁO LỊCH_SỬ GIA_ĐÌNH CỘNG_ĐỒNG ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐÁ BIỂN ĐẸP HOANG_SƠ HÙNG_VĨ GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI BÌNH_MINH HOÀNG_HÔN NGOÀI_TRỜI ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ CÂU_CÁ LÀNG_CHÀI PHONG_CẢNH ĐẸP HOANG_SƠ YÊN_BÌNH DÂN_GIAN GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI BÌNH_MINH HOÀNG_HÔN NGOÀI_TRỜI DI_SẢN ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ PHONG_CẢNH ĐẸP CỔ_XƯA LỊCH_SỬ VĂN_HÓA GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI NGOÀI_TRỜI DI_SẢN ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ LEO_NÚI CẮM_TRẠI NÚI PHONG_CẢNH ĐẸP HOANG_SƠ HÙNG_VĨ GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI BÌNH_MINH HOÀNG_HÔN NGOÀI_TRỜI ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>BƠI_LỘI CÂU_CÁ CHỤP_ẢNH ĐI_BỘ LẶN BIỂN CÁT ĐÁ THIÊN_NHIÊN ĐẸP HOANG_SƠ BÍ_ẨN DÂN_GIAN NHÀ_HÀNG GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI BÌNH_MINH HOÀNG_HÔN NGOÀI_TRỜI BÌNH_DÂN DI_SẢN ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>BƠI_LỘI CÂU_CÁ CHỤP_ẢNH ĐI_BỘ LẶN BIỂN CÁT ĐÁ THIÊN_NHIÊN ĐẸP HOANG_SƠ HÙNG_VĨ GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI BÌNH_MINH HOÀNG_HÔN NGOÀI_TRỜI ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ ĐẸP LỊCH_SỬ DÂN_TỘC LỄ_HỘI GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI NGOÀI_TRỜI DI_SẢN DI_TÍCH TÔN_GIÁO ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ PHONG_CẢNH ĐẸP HÙNG_VĨ CỔ_XƯA LỊCH_SỬ NGHỆ_THUẬT TÂM_LINH GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI DU_LỊCH DI_TÍCH KIẾN_TRÚC ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>LEO_NÚI CẮM_TRẠI VUI_CHƠI BIỂN NÚI ĐẸP HOANG_SƠ THỂ_THAO NHÀ_HÀNG CÀ_PHÊ CÔNG_VIÊN GIA_ĐÌNH TRẺ_EM BẠN_BÈ CUỐI_TUẦN ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ CÂU_CÁ PHONG_CẢNH ĐẸP HOANG_SƠ YÊN_BÌNH GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI BÌNH_MINH HOÀNG_HÔN NGOÀI_TRỜI ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ CÂU_CÁ CẮM_TRẠI BIỂN PHONG_CẢNH ĐẸP HOANG_SƠ YÊN_BÌNH GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI BÌNH_MINH HOÀNG_HÔN NGOÀI_TRỜI ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>CHỤP_ẢNH ĐI_BỘ CÂU_CÁ CẮM_TRẠI PHONG_CẢNH ĐẸP HOANG_SƠ YÊN_BÌNH GIA_ĐÌNH BẠN_BÈ CẶP_ĐÔI BÌNH_MINH HOÀNG_HÔN NGOÀI_TRỜI ĐỊA_ĐIỂM</t>
+  </si>
+  <si>
+    <t>TRẢI_NGHIỆM ĐỊA_ĐIỂM BIỂN DU_LỊCH VĂN_HÓA ẨM_THỰC LỊCH_SỬ NÚI HOẠT_ĐỘNG ĐẸP THƯỞNG_THỨC CẮM_TRẠI THIÊN_NHIÊN KHÁCH_SẠN VUI_CHƠI ĐỘC_ĐÁO TRUYỀN_THỐNG PHONG_CẢNH THỂ_THAO DI_TÍCH THƯ_GIÃN CHÙA HẤP_DẪN NỔI_TIẾNG ĐẶC_BIỆT ĐỊA_PHƯƠNG GIA_ĐÌNH YÊN_BÌNH ĐẶC_SẢN NGON CÀ_PHÊ BÌNH_DÂN MẠO_HIỂM NGHỆ_THUẬT BẠN_BÈ BÌNH_MINH HOANG_SƠ LẶN LỄ_HỘI NGHỈ_DƯỠNG PHƯỢT CỔ_XƯA DI_CHUYỂN LÀNG BƠI_LỘI DÂN_GIAN TÂM_LINH TOUR CON_ĐƯỜNG ĐÊM KIẾN_TRÚC CHỤP_ẢNH HẢI_SẢN SỰ_KIỆN HOÀNG_HÔN LÀNG_CHÀI LÃNG_MẠN RESORT CAO_CẤP SAN_HÔ THÀNH_PHỐ TRẺ_EM BIỂU_DIỄN CẶP_ĐÔI CỬA_HÀNG DI_SẢN NGOÀI_TRỜI CÂU_CÁ BẢO_TỒN CỘNG_ĐỒNG ĐÁ ĐỀN_THỜ ĐI_BỘ LEO_NÚI NHÀ_HÀNG NHÀ_NGHỈ NHỘN_NHỊP THUYỀN BẢO_TÀNG CÁT ĐÈO HANG_ĐỘNG HIỆN_ĐẠI HÒN_ĐẢO KHÓ_QUÊN LƯỚT_SÓNG TỰ_TÚC CHỢ CUỐI_TUẦN ĐỘNG_VẬT NGOẠI_Ô QUỐC_TẾ SUỐI VƯỜN_HOA RIÊNG_TƯ BÃI_CỎ DÂN_TỘC HỒ_THỦY_ĐIỆN HÙNG_VĨ KHOA_HỌC QUẢNG_TRƯỜNG THÁC_NƯỚC CÔNG_VIÊN BÍ_ẨN HỘI_THẢO SÂN_BAY TÔN_GIÁO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -487,6 +507,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111111"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="5">
@@ -543,7 +575,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -558,6 +590,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -860,17 +894,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.23046875" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="3" width="123.765625" customWidth="1"/>
-    <col min="4" max="4" width="22.69140625" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" customWidth="1"/>
+    <col min="3" max="3" width="123.77734375" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -884,514 +918,559 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C2" t="s">
-        <v>107</v>
+      <c r="C2" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A22" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C23" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="C34" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="C35" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D38" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C15" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="C39" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A19" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C20" t="s">
-        <v>123</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" t="s">
-        <v>124</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" t="s">
-        <v>125</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" t="s">
-        <v>126</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" t="s">
-        <v>127</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C28" t="s">
-        <v>130</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" t="s">
-        <v>135</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" t="s">
-        <v>131</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C32" t="s">
-        <v>142</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" t="s">
-        <v>136</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" t="s">
-        <v>137</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C35" t="s">
-        <v>144</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C36" t="s">
-        <v>140</v>
-      </c>
-      <c r="D36" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
+    <row r="40" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B40" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C37" t="s">
-        <v>138</v>
-      </c>
-      <c r="D37" s="3" t="s">
+      <c r="C40" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>94</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D10" r:id="rId1" xr:uid="{4B3BF609-731C-41A3-BFB2-9C4B107927DE}"/>
+    <hyperlink ref="D11" r:id="rId1"/>
+    <hyperlink ref="D3" r:id="rId2"/>
+    <hyperlink ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>